--- a/list-view-testcases.xlsx
+++ b/list-view-testcases.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Upload Check" sheetId="1" r:id="R9cad6a65db1145f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Cases" sheetId="1" r:id="Ra06bd3b46c0e4cda"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,7 +13,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="2">
+  <x:fonts count="3">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -22,15 +22,40 @@
       <x:b/>
       <x:sz val="11"/>
       <x:color rgb="FF000000"/>
-      <x:name val="Carlito"/>
+      <x:name val="Aptos Narrow"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF242424"/>
+      <x:name val="Aptos Narrow"/>
     </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="7">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="gray125"/>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFE600"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF5CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF5CC"/>
+      </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
@@ -45,16 +70,101 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="4">
+  <x:cellXfs count="29">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
 </x:styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BigBirdTestCases" displayName="BigBirdTestCases" ref="A1:L64" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="12">
+    <x:tableColumn id="1" name="ID"/>
+    <x:tableColumn id="2" name="Labels"/>
+    <x:tableColumn id="3" name="Lan"/>
+    <x:tableColumn id="4" name="Test Summary"/>
+    <x:tableColumn id="5" name="Description"/>
+    <x:tableColumn id="6" name="Action"/>
+    <x:tableColumn id="7" name="Expected Result"/>
+    <x:tableColumn id="8" name="Data"/>
+    <x:tableColumn id="9" name="Auto/ Assessment"/>
+    <x:tableColumn id="10" name="POD"/>
+    <x:tableColumn id="11" name="MALCODE"/>
+    <x:tableColumn id="12" name="Test Repository Path"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -252,27 +362,3212 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="65" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="38" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="12" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="21" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="10" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="76" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="67" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="65" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="78" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="58" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="22" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="17" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="16" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="32" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="27" customHeight="1">
-      <x:c r="A1" s="3" t="str">
-        <x:v>GitHub branch upload test</x:v>
-      </x:c>
-      <x:c r="B1" s="3" t="str">
-        <x:v>Status</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" t="str">
-        <x:v>Excel upload verification only — no internal test cases</x:v>
-      </x:c>
-      <x:c r="B2" t="str">
-        <x:v>No confidential data included</x:v>
-      </x:c>
+    <x:row r="1" ht="34" customHeight="1">
+      <x:c r="A1" s="28" t="str">
+        <x:v>ID</x:v>
+      </x:c>
+      <x:c r="B1" s="28" t="str">
+        <x:v>Labels</x:v>
+      </x:c>
+      <x:c r="C1" s="28" t="str">
+        <x:v>Lan</x:v>
+      </x:c>
+      <x:c r="D1" s="28" t="str">
+        <x:v>Test Summary</x:v>
+      </x:c>
+      <x:c r="E1" s="28" t="str">
+        <x:v>Description</x:v>
+      </x:c>
+      <x:c r="F1" s="28" t="str">
+        <x:v>Action</x:v>
+      </x:c>
+      <x:c r="G1" s="28" t="str">
+        <x:v>Expected Result</x:v>
+      </x:c>
+      <x:c r="H1" s="28" t="str">
+        <x:v>Data</x:v>
+      </x:c>
+      <x:c r="I1" s="28" t="str">
+        <x:v>Auto/ Assessment</x:v>
+      </x:c>
+      <x:c r="J1" s="28" t="str">
+        <x:v>POD</x:v>
+      </x:c>
+      <x:c r="K1" s="28" t="str">
+        <x:v>MALCODE</x:v>
+      </x:c>
+      <x:c r="L1" s="28" t="str">
+        <x:v>Test Repository Path</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="130" customHeight="1">
+      <x:c r="A2" s="25" t="str">
+        <x:v>TC-001</x:v>
+      </x:c>
+      <x:c r="B2" s="25" t="str">
+        <x:v>BIGBIRD-3029</x:v>
+      </x:c>
+      <x:c r="C2" s="27" t="str">
+        <x:v>EN</x:v>
+      </x:c>
+      <x:c r="D2" s="26" t="str">
+        <x:v>RetailRB_En_BM_LeadsListView_BranchClosedLeads_PreProductLeadFilter</x:v>
+      </x:c>
+      <x:c r="E2" s="26" t="str">
+        <x:v>Verify that the English Retail Manager user can access the Branch Closed Leads list view and that the Lead Sub Source filter is replaced with the Pre-Product Lead filter where applicable to Marketing leads.</x:v>
+      </x:c>
+      <x:c r="F2" s="26" t="str">
+        <x:v>Given Retail Manager is logged into RB as EN.
+When the user navigates to the Leads object.
+And the user opens the list view selector.
+And the user selects the "Branch Closed Leads" list view.
+And the user opens the Filters panel.</x:v>
+      </x:c>
+      <x:c r="G2" s="26" t="str">
+        <x:v>Then the "Branch Closed Leads" list view should load successfully and be accessible to the user.
+And the existing filter "Lead Sub Source not equal to PTYA" should be removed.
+And the new filter "Pre-Product Lead equals false" should be present for the applicable Marketing records.
+And the list view should display only records satisfying the updated filter criteria and all other existing filters.</x:v>
+      </x:c>
+      <x:c r="H2" s="26" t="str">
+        <x:v>User Coverage: English Retail Manager
+Shared With: English Branch Manager Users Group
+Object: Leads
+List View: Branch Closed Leads
+List View API Name: Branch_Closed_Leads
+Record Type: Marketing (where applicable)
+Removed Filter: Lead Sub Source != PTYA
+New Filter: Pre-Product Lead = false</x:v>
+      </x:c>
+      <x:c r="I2" s="25" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="J2" s="25" t="str">
+        <x:v>Batman</x:v>
+      </x:c>
+      <x:c r="K2" s="25" t="str">
+        <x:v>HOJ</x:v>
+      </x:c>
+      <x:c r="L2" s="26" t="str"/>
+    </x:row>
+    <x:row r="3" ht="130" customHeight="1">
+      <x:c r="A3" s="25" t="str">
+        <x:v>TC-002</x:v>
+      </x:c>
+      <x:c r="B3" s="25" t="str">
+        <x:v>BIGBIRD-3029</x:v>
+      </x:c>
+      <x:c r="C3" s="27" t="str">
+        <x:v>EN</x:v>
+      </x:c>
+      <x:c r="D3" s="26" t="str">
+        <x:v>RetailRB_En_Admin_LeadsListView_BranchClosedLeads_PreProductLeadFilter</x:v>
+      </x:c>
+      <x:c r="E3" s="26" t="str">
+        <x:v>Verify that the English Retail Admin user can access the Branch Closed Leads list view and that the Lead Sub Source filter is replaced with the Pre-Product Lead filter where applicable to Marketing leads.</x:v>
+      </x:c>
+      <x:c r="F3" s="26" t="str">
+        <x:v>Given Retail Admin is logged into RB as EN.
+When the user navigates to the Leads object.
+And the user opens the list view selector.
+And the user selects the "Branch Closed Leads" list view.
+And the user opens the Filters panel.</x:v>
+      </x:c>
+      <x:c r="G3" s="26" t="str">
+        <x:v>Then the "Branch Closed Leads" list view should load successfully and be accessible to the user.
+And the existing filter "Lead Sub Source not equal to PTYA" should be removed.
+And the new filter "Pre-Product Lead equals false" should be present for the applicable Marketing records.
+And the list view should display only records satisfying the updated filter criteria and all other existing filters.</x:v>
+      </x:c>
+      <x:c r="H3" s="26" t="str">
+        <x:v>User Coverage: English Retail Admin
+Shared With: English Business Admins Group
+Object: Leads
+List View: Branch Closed Leads
+List View API Name: Branch_Closed_Leads
+Record Type: Marketing (where applicable)
+Removed Filter: Lead Sub Source != PTYA
+New Filter: Pre-Product Lead = false</x:v>
+      </x:c>
+      <x:c r="I3" s="25" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="J3" s="25" t="str">
+        <x:v>Batman</x:v>
+      </x:c>
+      <x:c r="K3" s="25" t="str">
+        <x:v>HOJ</x:v>
+      </x:c>
+      <x:c r="L3" s="26" t="str"/>
+    </x:row>
+    <x:row r="4" ht="130" customHeight="1">
+      <x:c r="A4" s="25" t="str">
+        <x:v>TC-003</x:v>
+      </x:c>
+      <x:c r="B4" s="25" t="str">
+        <x:v>BIGBIRD-3029</x:v>
+      </x:c>
+      <x:c r="C4" s="27" t="str">
+        <x:v>EN</x:v>
+      </x:c>
+      <x:c r="D4" s="26" t="str">
+        <x:v>RetailRB_En_PBA_LeadsListView_CRMMyLeads_PreProductLeadFilter</x:v>
+      </x:c>
+      <x:c r="E4" s="26" t="str">
+        <x:v>Verify that the English Retail PBA user can access the My Leads list view and that the Lead Sub Source filter is replaced with the Pre-Product Lead filter where applicable to Marketing leads.</x:v>
+      </x:c>
+      <x:c r="F4" s="26" t="str">
+        <x:v>Given Retail PBA is logged into RB as EN.
+When the user navigates to the Leads object.
+And the user opens the list view selector.
+And the user selects the "My Leads" list view.
+And the user opens the Filters panel.</x:v>
+      </x:c>
+      <x:c r="G4" s="26" t="str">
+        <x:v>Then the "My Leads" list view should load successfully and be accessible to the user.
+And the existing filter "Lead Sub Source not equal to PTYA" should be removed.
+And the new filter "Pre-Product Lead equals false" should be present for the applicable Marketing records.
+And the list view should display only records satisfying the updated filter criteria and all other existing filters.</x:v>
+      </x:c>
+      <x:c r="H4" s="26" t="str">
+        <x:v>User Coverage: English Retail PBA
+Shared With: English Branch Advisor Users Group
+Object: Leads
+List View: My Leads
+List View API Name: CRM_My_Leads
+Record Type: Marketing (where applicable)
+Removed Filter: Lead Sub Source != PTYA
+New Filter: Pre-Product Lead = false</x:v>
+      </x:c>
+      <x:c r="I4" s="25" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="J4" s="25" t="str">
+        <x:v>Batman</x:v>
+      </x:c>
+      <x:c r="K4" s="25" t="str">
+        <x:v>HOJ</x:v>
+      </x:c>
+      <x:c r="L4" s="26" t="str"/>
+    </x:row>
+    <x:row r="5" ht="130" customHeight="1">
+      <x:c r="A5" s="25" t="str">
+        <x:v>TC-004</x:v>
+      </x:c>
+      <x:c r="B5" s="25" t="str">
+        <x:v>BIGBIRD-3029</x:v>
+      </x:c>
+      <x:c r="C5" s="27" t="str">
+        <x:v>EN</x:v>
+      </x:c>
+      <x:c r="D5" s="26" t="str">
+        <x:v>RetailRB_En_BM_LeadsListView_CRMMyLeads_PreProductLeadFilter</x:v>
+      </x:c>
+      <x:c r="E5" s="26" t="str">
+        <x:v>Verify that the English Retail Manager user can access the My Leads list view and that the Lead Sub Source filter is replaced with the Pre-Product Lead filter where applicable to Marketing leads.</x:v>
+      </x:c>
+      <x:c r="F5" s="26" t="str">
+        <x:v>Given Retail Manager is logged into RB as EN.
+When the user navigates to the Leads object.
+And the user opens the list view selector.
+And the user selects the "My Leads" list view.
+And the user opens the Filters panel.</x:v>
+      </x:c>
+      <x:c r="G5" s="26" t="str">
+        <x:v>Then the "My Leads" list view should load successfully and be accessible to the user.
+And the existing filter "Lead Sub Source not equal to PTYA" should be removed.
+And the new filter "Pre-Product Lead equals false" should be present for the applicable Marketing records.
+And the list view should display only records satisfying the updated filter criteria and all other existing filters.</x:v>
+      </x:c>
+      <x:c r="H5" s="26" t="str">
+        <x:v>User Coverage: English Retail Manager
+Shared With: English Branch Manager Users Group
+Object: Leads
+List View: My Leads
+List View API Name: CRM_My_Leads
+Record Type: Marketing (where applicable)
+Removed Filter: Lead Sub Source != PTYA
+New Filter: Pre-Product Lead = false</x:v>
+      </x:c>
+      <x:c r="I5" s="25" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="J5" s="25" t="str">
+        <x:v>Batman</x:v>
+      </x:c>
+      <x:c r="K5" s="25" t="str">
+        <x:v>HOJ</x:v>
+      </x:c>
+      <x:c r="L5" s="26" t="str"/>
+    </x:row>
+    <x:row r="6" ht="130" customHeight="1">
+      <x:c r="A6" s="25" t="str">
+        <x:v>TC-005</x:v>
+      </x:c>
+      <x:c r="B6" s="25" t="str">
+        <x:v>BIGBIRD-3029</x:v>
+      </x:c>
+      <x:c r="C6" s="27" t="str">
+        <x:v>EN</x:v>
+      </x:c>
+      <x:c r="D6" s="26" t="str">
+        <x:v>RetailRB_En_Admin_LeadsListView_CRMMyLeads_PreProductLeadFilter</x:v>
+      </x:c>
+      <x:c r="E6" s="26" t="str">
+        <x:v>Verify that the English Retail Admin user can access the My Leads list view and that the Lead Sub Source filter is replaced with the Pre-Product Lead filter where applicable to Marketing leads.</x:v>
+      </x:c>
+      <x:c r="F6" s="26" t="str">
+        <x:v>Given Retail Admin is logged into RB as EN.
+When the user navigates to the Leads object.
+And the user opens the list view selector.
+And the user selects the "My Leads" list view.
+And the user opens the Filters panel.</x:v>
+      </x:c>
+      <x:c r="G6" s="26" t="str">
+        <x:v>Then the "My Leads" list view should load successfully and be accessible to the user.
+And the existing filter "Lead Sub Source not equal to PTYA" should be removed.
+And the new filter "Pre-Product Lead equals false" should be present for the applicable Marketing records.
+And the list view should display only records satisfying the updated filter criteria and all other existing filters.</x:v>
+      </x:c>
+      <x:c r="H6" s="26" t="str">
+        <x:v>User Coverage: English Retail Admin
+Shared With: English Business Admins Group
+Object: Leads
+List View: My Leads
+List View API Name: CRM_My_Leads
+Record Type: Marketing (where applicable)
+Removed Filter: Lead Sub Source != PTYA
+New Filter: Pre-Product Lead = false</x:v>
+      </x:c>
+      <x:c r="I6" s="25" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="J6" s="25" t="str">
+        <x:v>Batman</x:v>
+      </x:c>
+      <x:c r="K6" s="25" t="str">
+        <x:v>HOJ</x:v>
+      </x:c>
+      <x:c r="L6" s="26" t="str"/>
+    </x:row>
+    <x:row r="7" ht="130" customHeight="1">
+      <x:c r="A7" s="25" t="str">
+        <x:v>TC-006</x:v>
+      </x:c>
+      <x:c r="B7" s="25" t="str">
+        <x:v>BIGBIRD-3029</x:v>
+      </x:c>
+      <x:c r="C7" s="27" t="str">
+        <x:v>FR</x:v>
+      </x:c>
+      <x:c r="D7" s="26" t="str">
+        <x:v>RetailRB_Fr_Admin_LeadsListView_ExceptionsParmiLesPistes_PreProductLeadFilter</x:v>
+      </x:c>
+      <x:c r="E7" s="26" t="str">
+        <x:v>Verify that the French Retail Admin user can access the Exceptions parmi les pistes list view and that the Lead Sub Source filter is replaced with the Pre-Product Lead filter where applicable to Marketing leads.</x:v>
+      </x:c>
+      <x:c r="F7" s="26" t="str">
+        <x:v>Given Retail Admin is logged into RB as FR.
+When the user navigates to the Leads object.
+And the user opens the list view selector.
+And the user selects the "Exceptions parmi les pistes" list view.
+And the user opens the Filters panel.</x:v>
+      </x:c>
+      <x:c r="G7" s="26" t="str">
+        <x:v>Then the "Exceptions parmi les pistes" list view should load successfully and be accessible to the user.
+And the existing filter "Lead Sub Source not equal to PTYA" should be removed.
+And the new filter "Pre-Product Lead equals false" should be present for the applicable Marketing records.
+And the list view should display only records satisfying the updated filter criteria and all other existing filters.</x:v>
+      </x:c>
+      <x:c r="H7" s="26" t="str">
+        <x:v>User Coverage: French Retail Admin
+Shared With: French Business Admins Group
+Object: Leads
+List View: Exceptions parmi les pistes
+List View API Name: Exceptions_parmi_les_pistes
+Record Type: Marketing (where applicable)
+Removed Filter: Lead Sub Source != PTYA
+New Filter: Pre-Product Lead = false</x:v>
+      </x:c>
+      <x:c r="I7" s="25" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="J7" s="25" t="str">
+        <x:v>Batman</x:v>
+      </x:c>
+      <x:c r="K7" s="25" t="str">
+        <x:v>HOJ</x:v>
+      </x:c>
+      <x:c r="L7" s="26" t="str"/>
+    </x:row>
+    <x:row r="8" ht="130" customHeight="1">
+      <x:c r="A8" s="25" t="str">
+        <x:v>TC-007</x:v>
+      </x:c>
+      <x:c r="B8" s="25" t="str">
+        <x:v>BIGBIRD-3029</x:v>
+      </x:c>
+      <x:c r="C8" s="27" t="str">
+        <x:v>FR</x:v>
+      </x:c>
+      <x:c r="D8" s="26" t="str">
+        <x:v>RetailRB_Fr_MarketingUser_LeadsListView_ExceptionsParmiLesPistes_PreProductLeadFilter</x:v>
+      </x:c>
+      <x:c r="E8" s="26" t="str">
+        <x:v>Verify that the French Marketing User user can access the Exceptions parmi les pistes list view and that the Lead Sub Source filter is replaced with the Pre-Product Lead filter where applicable to Marketing leads.</x:v>
+      </x:c>
+      <x:c r="F8" s="26" t="str">
+        <x:v>Given Marketing User is logged into RB as FR.
+When the user navigates to the Leads object.
+And the user opens the list view selector.
+And the user selects the "Exceptions parmi les pistes" list view.
+And the user opens the Filters panel.</x:v>
+      </x:c>
+      <x:c r="G8" s="26" t="str">
+        <x:v>Then the "Exceptions parmi les pistes" list view should load successfully and be accessible to the user.
+And the existing filter "Lead Sub Source not equal to PTYA" should be removed.
+And the new filter "Pre-Product Lead equals false" should be present for the applicable Marketing records.
+And the list view should display only records satisfying the updated filter criteria and all other existing filters.</x:v>
+      </x:c>
+      <x:c r="H8" s="26" t="str">
+        <x:v>User Coverage: French Marketing User
+Shared With: French Marketing User Group
+Object: Leads
+List View: Exceptions parmi les pistes
+List View API Name: Exceptions_parmi_les_pistes
+Record Type: Marketing (where applicable)
+Removed Filter: Lead Sub Source != PTYA
+New Filter: Pre-Product Lead = false</x:v>
+      </x:c>
+      <x:c r="I8" s="25" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="J8" s="25" t="str">
+        <x:v>Batman</x:v>
+      </x:c>
+      <x:c r="K8" s="25" t="str">
+        <x:v>HOJ</x:v>
+      </x:c>
+      <x:c r="L8" s="26" t="str"/>
+    </x:row>
+    <x:row r="9" ht="130" customHeight="1">
+      <x:c r="A9" s="25" t="str">
+        <x:v>TC-008</x:v>
+      </x:c>
+      <x:c r="B9" s="25" t="str">
+        <x:v>BIGBIRD-3029</x:v>
+      </x:c>
+      <x:c r="C9" s="27" t="str">
+        <x:v>FR</x:v>
+      </x:c>
+      <x:c r="D9" s="26" t="str">
+        <x:v>RetailRB_Fr_Admin_LeadsListView_ExceptionsParmiLesRecommandations_PreProductLeadFilter</x:v>
+      </x:c>
+      <x:c r="E9" s="26" t="str">
+        <x:v>Verify that the French Retail Admin user can access the Exceptions parmi les recommandations list view and that the Lead Sub Source filter is replaced with the Pre-Product Lead filter where applicable to Marketing leads.</x:v>
+      </x:c>
+      <x:c r="F9" s="26" t="str">
+        <x:v>Given Retail Admin is logged into RB as FR.
+When the user navigates to the Leads object.
+And the user opens the list view selector.
+And the user selects the "Exceptions parmi les recommandations" list view.
+And the user opens the Filters panel.</x:v>
+      </x:c>
+      <x:c r="G9" s="26" t="str">
+        <x:v>Then the "Exceptions parmi les recommandations" list view should load successfully and be accessible to the user.
+And the existing filter "Lead Sub Source not equal to PTYA" should be removed.
+And the new filter "Pre-Product Lead equals false" should be present for the applicable Marketing records.
+And the list view should display only records satisfying the updated filter criteria and all other existing filters.</x:v>
+      </x:c>
+      <x:c r="H9" s="26" t="str">
+        <x:v>User Coverage: French Retail Admin
+Shared With: French Business Admins Group
+Object: Leads
+List View: Exceptions parmi les recommandations
+List View API Name: Exceptions_parmi_les_recommandations
+Record Type: Marketing (where applicable)
+Removed Filter: Lead Sub Source != PTYA
+New Filter: Pre-Product Lead = false</x:v>
+      </x:c>
+      <x:c r="I9" s="25" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="J9" s="25" t="str">
+        <x:v>Batman</x:v>
+      </x:c>
+      <x:c r="K9" s="25" t="str">
+        <x:v>HOJ</x:v>
+      </x:c>
+      <x:c r="L9" s="26" t="str"/>
+    </x:row>
+    <x:row r="10" ht="130" customHeight="1">
+      <x:c r="A10" s="25" t="str">
+        <x:v>TC-009</x:v>
+      </x:c>
+      <x:c r="B10" s="25" t="str">
+        <x:v>BIGBIRD-3029</x:v>
+      </x:c>
+      <x:c r="C10" s="27" t="str">
+        <x:v>FR</x:v>
+      </x:c>
+      <x:c r="D10" s="26" t="str">
+        <x:v>RetailRB_Fr_MarketingUser_LeadsListView_ExceptionsParmiLesRecommandations_PreProductLeadFilter</x:v>
+      </x:c>
+      <x:c r="E10" s="26" t="str">
+        <x:v>Verify that the French Marketing User user can access the Exceptions parmi les recommandations list view and that the Lead Sub Source filter is replaced with the Pre-Product Lead filter where applicable to Marketing leads.</x:v>
+      </x:c>
+      <x:c r="F10" s="26" t="str">
+        <x:v>Given Marketing User is logged into RB as FR.
+When the user navigates to the Leads object.
+And the user opens the list view selector.
+And the user selects the "Exceptions parmi les recommandations" list view.
+And the user opens the Filters panel.</x:v>
+      </x:c>
+      <x:c r="G10" s="26" t="str">
+        <x:v>Then the "Exceptions parmi les recommandations" list view should load successfully and be accessible to the user.
+And the existing filter "Lead Sub Source not equal to PTYA" should be removed.
+And the new filter "Pre-Product Lead equals false" should be present for the applicable Marketing records.
+And the list view should display only records satisfying the updated filter criteria and all other existing filters.</x:v>
+      </x:c>
+      <x:c r="H10" s="26" t="str">
+        <x:v>User Coverage: French Marketing User
+Shared With: French Marketing User Group
+Object: Leads
+List View: Exceptions parmi les recommandations
+List View API Name: Exceptions_parmi_les_recommandations
+Record Type: Marketing (where applicable)
+Removed Filter: Lead Sub Source != PTYA
+New Filter: Pre-Product Lead = false</x:v>
+      </x:c>
+      <x:c r="I10" s="25" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="J10" s="25" t="str">
+        <x:v>Batman</x:v>
+      </x:c>
+      <x:c r="K10" s="25" t="str">
+        <x:v>HOJ</x:v>
+      </x:c>
+      <x:c r="L10" s="26" t="str"/>
+    </x:row>
+    <x:row r="11" ht="130" customHeight="1">
+      <x:c r="A11" s="25" t="str">
+        <x:v>TC-010</x:v>
+      </x:c>
+      <x:c r="B11" s="25" t="str">
+        <x:v>BIGBIRD-3029</x:v>
+      </x:c>
+      <x:c r="C11" s="27" t="str">
+        <x:v>FR</x:v>
+      </x:c>
+      <x:c r="D11" s="26" t="str">
+        <x:v>RetailRB_Fr_PBA_LeadsListView_MesPistes_PreProductLeadFilter</x:v>
+      </x:c>
+      <x:c r="E11" s="26" t="str">
+        <x:v>Verify that the French Retail PBA user can access the Mes pistes list view and that the Lead Sub Source filter is replaced with the Pre-Product Lead filter where applicable to Marketing leads.</x:v>
+      </x:c>
+      <x:c r="F11" s="26" t="str">
+        <x:v>Given Retail PBA is logged into RB as FR.
+When the user navigates to the Leads object.
+And the user opens the list view selector.
+And the user selects the "Mes pistes" list view.
+And the user opens the Filters panel.</x:v>
+      </x:c>
+      <x:c r="G11" s="26" t="str">
+        <x:v>Then the "Mes pistes" list view should load successfully and be accessible to the user.
+And the existing filter "Lead Sub Source not equal to PTYA" should be removed.
+And the new filter "Pre-Product Lead equals false" should be present for the applicable Marketing records.
+And the list view should display only records satisfying the updated filter criteria and all other existing filters.</x:v>
+      </x:c>
+      <x:c r="H11" s="26" t="str">
+        <x:v>User Coverage: French Retail PBA
+Shared With: French Branch Advisor Users Group
+Object: Leads
+List View: Mes pistes
+List View API Name: Mes_pistes
+Record Type: Marketing (where applicable)
+Removed Filter: Lead Sub Source != PTYA
+New Filter: Pre-Product Lead = false</x:v>
+      </x:c>
+      <x:c r="I11" s="25" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="J11" s="25" t="str">
+        <x:v>Batman</x:v>
+      </x:c>
+      <x:c r="K11" s="25" t="str">
+        <x:v>HOJ</x:v>
+      </x:c>
+      <x:c r="L11" s="26" t="str"/>
+    </x:row>
+    <x:row r="12" ht="130" customHeight="1">
+      <x:c r="A12" s="25" t="str">
+        <x:v>TC-011</x:v>
+      </x:c>
+      <x:c r="B12" s="25" t="str">
+        <x:v>BIGBIRD-3029</x:v>
+      </x:c>
+      <x:c r="C12" s="27" t="str">
+        <x:v>FR</x:v>
+      </x:c>
+      <x:c r="D12" s="26" t="str">
+        <x:v>RetailRB_Fr_BM_LeadsListView_MesPistes_PreProductLeadFilter</x:v>
+      </x:c>
+      <x:c r="E12" s="26" t="str">
+        <x:v>Verify that the French Retail Manager user can access the Mes pistes list view and that the Lead Sub Source filter is replaced with the Pre-Product Lead filter where applicable to Marketing leads.</x:v>
+      </x:c>
+      <x:c r="F12" s="26" t="str">
+        <x:v>Given Retail Manager is logged into RB as FR.
+When the user navigates to the Leads object.
+And the user opens the list view selector.
+And the user selects the "Mes pistes" list view.
+And the user opens the Filters panel.</x:v>
+      </x:c>
+      <x:c r="G12" s="26" t="str">
+        <x:v>Then the "Mes pistes" list view should load successfully and be accessible to the user.
+And the existing filter "Lead Sub Source not equal to PTYA" should be removed.
+And the new filter "Pre-Product Lead equals false" should be present for the applicable Marketing records.
+And the list view should display only records satisfying the updated filter criteria and all other existing filters.</x:v>
+      </x:c>
+      <x:c r="H12" s="26" t="str">
+        <x:v>User Coverage: French Retail Manager
+Shared With: French Branch Manager Users Group
+Object: Leads
+List View: Mes pistes
+List View API Name: Mes_pistes
+Record Type: Marketing (where applicable)
+Removed Filter: Lead Sub Source != PTYA
+New Filter: Pre-Product Lead = false</x:v>
+      </x:c>
+      <x:c r="I12" s="25" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="J12" s="25" t="str">
+        <x:v>Batman</x:v>
+      </x:c>
+      <x:c r="K12" s="25" t="str">
+        <x:v>HOJ</x:v>
+      </x:c>
+      <x:c r="L12" s="26" t="str"/>
+    </x:row>
+    <x:row r="13" ht="130" customHeight="1">
+      <x:c r="A13" s="25" t="str">
+        <x:v>TC-012</x:v>
+      </x:c>
+      <x:c r="B13" s="25" t="str">
+        <x:v>BIGBIRD-3029</x:v>
+      </x:c>
+      <x:c r="C13" s="27" t="str">
+        <x:v>FR</x:v>
+      </x:c>
+      <x:c r="D13" s="26" t="str">
+        <x:v>RetailRB_Fr_Admin_LeadsListView_MesPistes_PreProductLeadFilter</x:v>
+      </x:c>
+      <x:c r="E13" s="26" t="str">
+        <x:v>Verify that the French Retail Admin user can access the Mes pistes list view and that the Lead Sub Source filter is replaced with the Pre-Product Lead filter where applicable to Marketing leads.</x:v>
+      </x:c>
+      <x:c r="F13" s="26" t="str">
+        <x:v>Given Retail Admin is logged into RB as FR.
+When the user navigates to the Leads object.
+And the user opens the list view selector.
+And the user selects the "Mes pistes" list view.
+And the user opens the Filters panel.</x:v>
+      </x:c>
+      <x:c r="G13" s="26" t="str">
+        <x:v>Then the "Mes pistes" list view should load successfully and be accessible to the user.
+And the existing filter "Lead Sub Source not equal to PTYA" should be removed.
+And the new filter "Pre-Product Lead equals false" should be present for the applicable Marketing records.
+And the list view should display only records satisfying the updated filter criteria and all other existing filters.</x:v>
+      </x:c>
+      <x:c r="H13" s="26" t="str">
+        <x:v>User Coverage: French Retail Admin
+Shared With: French Business Admins Group
+Object: Leads
+List View: Mes pistes
+List View API Name: Mes_pistes
+Record Type: Marketing (where applicable)
+Removed Filter: Lead Sub Source != PTYA
+New Filter: Pre-Product Lead = false</x:v>
+      </x:c>
+      <x:c r="I13" s="25" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="J13" s="25" t="str">
+        <x:v>Batman</x:v>
+      </x:c>
+      <x:c r="K13" s="25" t="str">
+        <x:v>HOJ</x:v>
+      </x:c>
+      <x:c r="L13" s="26" t="str"/>
+    </x:row>
+    <x:row r="14" ht="130" customHeight="1">
+      <x:c r="A14" s="25" t="str">
+        <x:v>TC-013</x:v>
+      </x:c>
+      <x:c r="B14" s="25" t="str">
+        <x:v>BIGBIRD-3029</x:v>
+      </x:c>
+      <x:c r="C14" s="27" t="str">
+        <x:v>FR</x:v>
+      </x:c>
+      <x:c r="D14" s="26" t="str">
+        <x:v>RSGRB_Fr_TL_LeadsListView_MesPistesCreeParLUtilis_PreProductLeadFilter</x:v>
+      </x:c>
+      <x:c r="E14" s="26" t="str">
+        <x:v>Verify that the French RSG Team Leader user can access the Mes Pistes Créée par L'utilis list view and that the Lead Sub Source filter is replaced with the Pre-Product Lead filter where applicable to Marketing leads.</x:v>
+      </x:c>
+      <x:c r="F14" s="26" t="str">
+        <x:v>Given RSG Team Leader is logged into RB as FR.
+When the user navigates to the Leads object.
+And the user opens the list view selector.
+And the user selects the "Mes Pistes Créée par L'utilis" list view.
+And the user opens the Filters panel.</x:v>
+      </x:c>
+      <x:c r="G14" s="26" t="str">
+        <x:v>Then the "Mes Pistes Créée par L'utilis" list view should load successfully and be accessible to the user.
+And the existing filter "Lead Sub Source not equal to PTYA" should be removed.
+And the new filter "Pre-Product Lead equals false" should be present for the applicable Marketing records.
+And the list view should display only records satisfying the updated filter criteria and all other existing filters.</x:v>
+      </x:c>
+      <x:c r="H14" s="26" t="str">
+        <x:v>User Coverage: French RSG Team Leader
+Shared With: French PCMR Manager Users Group
+Object: Leads
+List View: Mes Pistes Créée par L'utilis
+List View API Name: Mes_Pistes_Cr_e_par_L_utilis
+Record Type: Marketing (where applicable)
+Removed Filter: Lead Sub Source != PTYA
+New Filter: Pre-Product Lead = false</x:v>
+      </x:c>
+      <x:c r="I14" s="25" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="J14" s="25" t="str">
+        <x:v>Batman</x:v>
+      </x:c>
+      <x:c r="K14" s="25" t="str">
+        <x:v>HOJ</x:v>
+      </x:c>
+      <x:c r="L14" s="26" t="str"/>
+    </x:row>
+    <x:row r="15" ht="130" customHeight="1">
+      <x:c r="A15" s="25" t="str">
+        <x:v>TC-014</x:v>
+      </x:c>
+      <x:c r="B15" s="25" t="str">
+        <x:v>BIGBIRD-3029</x:v>
+      </x:c>
+      <x:c r="C15" s="27" t="str">
+        <x:v>FR</x:v>
+      </x:c>
+      <x:c r="D15" s="26" t="str">
+        <x:v>RSGRB_Fr_PC_LeadsListView_MesPistesCreeParLUtilis_PreProductLeadFilter</x:v>
+      </x:c>
+      <x:c r="E15" s="26" t="str">
+        <x:v>Verify that the French RSG Phone Concierge user can access the Mes Pistes Créée par L'utilis list view and that the Lead Sub Source filter is replaced with the Pre-Product Lead filter where applicable to Marketing leads.</x:v>
+      </x:c>
+      <x:c r="F15" s="26" t="str">
+        <x:v>Given RSG Phone Concierge is logged into RB as FR.
+When the user navigates to the Leads object.
+And the user opens the list view selector.
+And the user selects the "Mes Pistes Créée par L'utilis" list view.
+And the user opens the Filters panel.</x:v>
+      </x:c>
+      <x:c r="G15" s="26" t="str">
+        <x:v>Then the "Mes Pistes Créée par L'utilis" list view should load successfully and be accessible to the user.
+And the existing filter "Lead Sub Source not equal to PTYA" should be removed.
+And the new filter "Pre-Product Lead equals false" should be present for the applicable Marketing records.
+And the list view should display only records satisfying the updated filter criteria and all other existing filters.</x:v>
+      </x:c>
+      <x:c r="H15" s="26" t="str">
+        <x:v>User Coverage: French RSG Phone Concierge
+Shared With: French Phone Concierge Users Group
+Object: Leads
+List View: Mes Pistes Créée par L'utilis
+List View API Name: Mes_Pistes_Cr_e_par_L_utilis
+Record Type: Marketing (where applicable)
+Removed Filter: Lead Sub Source != PTYA
+New Filter: Pre-Product Lead = false</x:v>
+      </x:c>
+      <x:c r="I15" s="25" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="J15" s="25" t="str">
+        <x:v>Batman</x:v>
+      </x:c>
+      <x:c r="K15" s="25" t="str">
+        <x:v>HOJ</x:v>
+      </x:c>
+      <x:c r="L15" s="26" t="str"/>
+    </x:row>
+    <x:row r="16" ht="130" customHeight="1">
+      <x:c r="A16" s="25" t="str">
+        <x:v>TC-015</x:v>
+      </x:c>
+      <x:c r="B16" s="25" t="str">
+        <x:v>BIGBIRD-3029</x:v>
+      </x:c>
+      <x:c r="C16" s="27" t="str">
+        <x:v>FR</x:v>
+      </x:c>
+      <x:c r="D16" s="26" t="str">
+        <x:v>RetailRB_Fr_PBA_LeadsListView_MesPistesFermees_PreProductLeadFilter</x:v>
+      </x:c>
+      <x:c r="E16" s="26" t="str">
+        <x:v>Verify that the French Retail PBA user can access the Mes pistes fermées list view and that the Lead Sub Source filter is replaced with the Pre-Product Lead filter where applicable to Marketing leads.</x:v>
+      </x:c>
+      <x:c r="F16" s="26" t="str">
+        <x:v>Given Retail PBA is logged into RB as FR.
+When the user navigates to the Leads object.
+And the user opens the list view selector.
+And the user selects the "Mes pistes fermées" list view.
+And the user opens the Filters panel.</x:v>
+      </x:c>
+      <x:c r="G16" s="26" t="str">
+        <x:v>Then the "Mes pistes fermées" list view should load successfully and be accessible to the user.
+And the existing filter "Lead Sub Source not equal to PTYA" should be removed.
+And the new filter "Pre-Product Lead equals false" should be present for the applicable Marketing records.
+And the list view should display only records satisfying the updated filter criteria and all other existing filters.</x:v>
+      </x:c>
+      <x:c r="H16" s="26" t="str">
+        <x:v>User Coverage: French Retail PBA
+Shared With: French Branch Advisor Users Group
+Object: Leads
+List View: Mes pistes fermées
+List View API Name: Mes_pistes_ferm_es
+Record Type: Marketing (where applicable)
+Removed Filter: Lead Sub Source != PTYA
+New Filter: Pre-Product Lead = false</x:v>
+      </x:c>
+      <x:c r="I16" s="25" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="J16" s="25" t="str">
+        <x:v>Batman</x:v>
+      </x:c>
+      <x:c r="K16" s="25" t="str">
+        <x:v>HOJ</x:v>
+      </x:c>
+      <x:c r="L16" s="26" t="str"/>
+    </x:row>
+    <x:row r="17" ht="130" customHeight="1">
+      <x:c r="A17" s="25" t="str">
+        <x:v>TC-016</x:v>
+      </x:c>
+      <x:c r="B17" s="25" t="str">
+        <x:v>BIGBIRD-3029</x:v>
+      </x:c>
+      <x:c r="C17" s="27" t="str">
+        <x:v>FR</x:v>
+      </x:c>
+      <x:c r="D17" s="26" t="str">
+        <x:v>RetailRB_Fr_BM_LeadsListView_MesPistesFermees_PreProductLeadFilter</x:v>
+      </x:c>
+      <x:c r="E17" s="26" t="str">
+        <x:v>Verify that the French Retail Manager user can access the Mes pistes fermées list view and that the Lead Sub Source filter is replaced with the Pre-Product Lead filter where applicable to Marketing leads.</x:v>
+      </x:c>
+      <x:c r="F17" s="26" t="str">
+        <x:v>Given Retail Manager is logged into RB as FR.
+When the user navigates to the Leads object.
+And the user opens the list view selector.
+And the user selects the "Mes pistes fermées" list view.
+And the user opens the Filters panel.</x:v>
+      </x:c>
+      <x:c r="G17" s="26" t="str">
+        <x:v>Then the "Mes pistes fermées" list view should load successfully and be accessible to the user.
+And the existing filter "Lead Sub Source not equal to PTYA" should be removed.
+And the new filter "Pre-Product Lead equals false" should be present for the applicable Marketing records.
+And the list view should display only records satisfying the updated filter criteria and all other existing filters.</x:v>
+      </x:c>
+      <x:c r="H17" s="26" t="str">
+        <x:v>User Coverage: French Retail Manager
+Shared With: French Branch Manager Users Group
+Object: Leads
+List View: Mes pistes fermées
+List View API Name: Mes_pistes_ferm_es
+Record Type: Marketing (where applicable)
+Removed Filter: Lead Sub Source != PTYA
+New Filter: Pre-Product Lead = false</x:v>
+      </x:c>
+      <x:c r="I17" s="25" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="J17" s="25" t="str">
+        <x:v>Batman</x:v>
+      </x:c>
+      <x:c r="K17" s="25" t="str">
+        <x:v>HOJ</x:v>
+      </x:c>
+      <x:c r="L17" s="26" t="str"/>
+    </x:row>
+    <x:row r="18" ht="130" customHeight="1">
+      <x:c r="A18" s="25" t="str">
+        <x:v>TC-017</x:v>
+      </x:c>
+      <x:c r="B18" s="25" t="str">
+        <x:v>BIGBIRD-3029</x:v>
+      </x:c>
+      <x:c r="C18" s="27" t="str">
+        <x:v>FR</x:v>
+      </x:c>
+      <x:c r="D18" s="26" t="str">
+        <x:v>RetailRB_Fr_Admin_LeadsListView_MesPistesFermees_PreProductLeadFilter</x:v>
+      </x:c>
+      <x:c r="E18" s="26" t="str">
+        <x:v>Verify that the French Retail Admin user can access the Mes pistes fermées list view and that the Lead Sub Source filter is replaced with the Pre-Product Lead filter where applicable to Marketing leads.</x:v>
+      </x:c>
+      <x:c r="F18" s="26" t="str">
+        <x:v>Given Retail Admin is logged into RB as FR.
+When the user navigates to the Leads object.
+And the user opens the list view selector.
+And the user selects the "Mes pistes fermées" list view.
+And the user opens the Filters panel.</x:v>
+      </x:c>
+      <x:c r="G18" s="26" t="str">
+        <x:v>Then the "Mes pistes fermées" list view should load successfully and be accessible to the user.
+And the existing filter "Lead Sub Source not equal to PTYA" should be removed.
+And the new filter "Pre-Product Lead equals false" should be present for the applicable Marketing records.
+And the list view should display only records satisfying the updated filter criteria and all other existing filters.</x:v>
+      </x:c>
+      <x:c r="H18" s="26" t="str">
+        <x:v>User Coverage: French Retail Admin
+Shared With: French Business Admins Group
+Object: Leads
+List View: Mes pistes fermées
+List View API Name: Mes_pistes_ferm_es
+Record Type: Marketing (where applicable)
+Removed Filter: Lead Sub Source != PTYA
+New Filter: Pre-Product Lead = false</x:v>
+      </x:c>
+      <x:c r="I18" s="25" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="J18" s="25" t="str">
+        <x:v>Batman</x:v>
+      </x:c>
+      <x:c r="K18" s="25" t="str">
+        <x:v>HOJ</x:v>
+      </x:c>
+      <x:c r="L18" s="26" t="str"/>
+    </x:row>
+    <x:row r="19" ht="130" customHeight="1">
+      <x:c r="A19" s="25" t="str">
+        <x:v>TC-018</x:v>
+      </x:c>
+      <x:c r="B19" s="25" t="str">
+        <x:v>BIGBIRD-3029</x:v>
+      </x:c>
+      <x:c r="C19" s="27" t="str">
+        <x:v>EN</x:v>
+      </x:c>
+      <x:c r="D19" s="26" t="str">
+        <x:v>RetailRB_En_SystemAdmin_LeadsListView_MyBranchMarketingLeads_PreProductLeadFilter</x:v>
+      </x:c>
+      <x:c r="E19" s="26" t="str">
+        <x:v>Verify that the English System Admin user can access the My Branch Marketing Leads list view and that the Lead Sub Source filter is replaced with the Pre-Product Lead filter where applicable to Marketing leads.</x:v>
+      </x:c>
+      <x:c r="F19" s="26" t="str">
+        <x:v>Given System Admin is logged into RB as EN.
+When the user navigates to the Leads object.
+And the user opens the list view selector.
+And the user selects the "My Branch Marketing Leads" list view.
+And the user opens the Filters panel.</x:v>
+      </x:c>
+      <x:c r="G19" s="26" t="str">
+        <x:v>Then the "My Branch Marketing Leads" list view should load successfully and be accessible to the user.
+And the existing filter "Lead Sub Source not equal to PTYA" should be removed.
+And the new filter "Pre-Product Lead equals false" should be present for the applicable Marketing records.
+And the list view should display only records satisfying the updated filter criteria and all other existing filters.</x:v>
+      </x:c>
+      <x:c r="H19" s="26" t="str">
+        <x:v>User Coverage: English System Admin
+Shared With: CEO (Roles)
+Object: Leads
+List View: My Branch Marketing Leads
+List View API Name: My_Branch_Marketing_Leads
+Record Type: Marketing (where applicable)
+Removed Filter: Lead Sub Source != PTYA
+New Filter: Pre-Product Lead = false</x:v>
+      </x:c>
+      <x:c r="I19" s="25" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="J19" s="25" t="str">
+        <x:v>Batman</x:v>
+      </x:c>
+      <x:c r="K19" s="25" t="str">
+        <x:v>HOJ</x:v>
+      </x:c>
+      <x:c r="L19" s="26" t="str"/>
+    </x:row>
+    <x:row r="20" ht="130" customHeight="1">
+      <x:c r="A20" s="25" t="str">
+        <x:v>TC-019</x:v>
+      </x:c>
+      <x:c r="B20" s="25" t="str">
+        <x:v>BIGBIRD-3029</x:v>
+      </x:c>
+      <x:c r="C20" s="27" t="str">
+        <x:v>EN</x:v>
+      </x:c>
+      <x:c r="D20" s="26" t="str">
+        <x:v>RetailRB_En_PBA_LeadsListView_MyClosedLeads_PreProductLeadFilter</x:v>
+      </x:c>
+      <x:c r="E20" s="26" t="str">
+        <x:v>Verify that the English Retail PBA user can access the My Closed Leads list view and that the Lead Sub Source filter is replaced with the Pre-Product Lead filter where applicable to Marketing leads.</x:v>
+      </x:c>
+      <x:c r="F20" s="26" t="str">
+        <x:v>Given Retail PBA is logged into RB as EN.
+When the user navigates to the Leads object.
+And the user opens the list view selector.
+And the user selects the "My Closed Leads" list view.
+And the user opens the Filters panel.</x:v>
+      </x:c>
+      <x:c r="G20" s="26" t="str">
+        <x:v>Then the "My Closed Leads" list view should load successfully and be accessible to the user.
+And the existing filter "Lead Sub Source not equal to PTYA" should be removed.
+And the new filter "Pre-Product Lead equals false" should be present for the applicable Marketing records.
+And the list view should display only records satisfying the updated filter criteria and all other existing filters.</x:v>
+      </x:c>
+      <x:c r="H20" s="26" t="str">
+        <x:v>User Coverage: English Retail PBA
+Shared With: English Branch Advisor Users Group
+Object: Leads
+List View: My Closed Leads
+List View API Name: My_Closed_Leads
+Record Type: Marketing (where applicable)
+Removed Filter: Lead Sub Source != PTYA
+New Filter: Pre-Product Lead = false</x:v>
+      </x:c>
+      <x:c r="I20" s="25" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="J20" s="25" t="str">
+        <x:v>Batman</x:v>
+      </x:c>
+      <x:c r="K20" s="25" t="str">
+        <x:v>HOJ</x:v>
+      </x:c>
+      <x:c r="L20" s="26" t="str"/>
+    </x:row>
+    <x:row r="21" ht="130" customHeight="1">
+      <x:c r="A21" s="25" t="str">
+        <x:v>TC-020</x:v>
+      </x:c>
+      <x:c r="B21" s="25" t="str">
+        <x:v>BIGBIRD-3029</x:v>
+      </x:c>
+      <x:c r="C21" s="27" t="str">
+        <x:v>EN</x:v>
+      </x:c>
+      <x:c r="D21" s="26" t="str">
+        <x:v>RetailRB_En_BM_LeadsListView_MyClosedLeads_PreProductLeadFilter</x:v>
+      </x:c>
+      <x:c r="E21" s="26" t="str">
+        <x:v>Verify that the English Retail Manager user can access the My Closed Leads list view and that the Lead Sub Source filter is replaced with the Pre-Product Lead filter where applicable to Marketing leads.</x:v>
+      </x:c>
+      <x:c r="F21" s="26" t="str">
+        <x:v>Given Retail Manager is logged into RB as EN.
+When the user navigates to the Leads object.
+And the user opens the list view selector.
+And the user selects the "My Closed Leads" list view.
+And the user opens the Filters panel.</x:v>
+      </x:c>
+      <x:c r="G21" s="26" t="str">
+        <x:v>Then the "My Closed Leads" list view should load successfully and be accessible to the user.
+And the existing filter "Lead Sub Source not equal to PTYA" should be removed.
+And the new filter "Pre-Product Lead equals false" should be present for the applicable Marketing records.
+And the list view should display only records satisfying the updated filter criteria and all other existing filters.</x:v>
+      </x:c>
+      <x:c r="H21" s="26" t="str">
+        <x:v>User Coverage: English Retail Manager
+Shared With: English Branch Manager Users Group
+Object: Leads
+List View: My Closed Leads
+List View API Name: My_Closed_Leads
+Record Type: Marketing (where applicable)
+Removed Filter: Lead Sub Source != PTYA
+New Filter: Pre-Product Lead = false</x:v>
+      </x:c>
+      <x:c r="I21" s="25" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="J21" s="25" t="str">
+        <x:v>Batman</x:v>
+      </x:c>
+      <x:c r="K21" s="25" t="str">
+        <x:v>HOJ</x:v>
+      </x:c>
+      <x:c r="L21" s="26" t="str"/>
+    </x:row>
+    <x:row r="22" ht="130" customHeight="1">
+      <x:c r="A22" s="25" t="str">
+        <x:v>TC-021</x:v>
+      </x:c>
+      <x:c r="B22" s="25" t="str">
+        <x:v>BIGBIRD-3029</x:v>
+      </x:c>
+      <x:c r="C22" s="27" t="str">
+        <x:v>EN</x:v>
+      </x:c>
+      <x:c r="D22" s="26" t="str">
+        <x:v>RetailRB_En_Admin_LeadsListView_MyClosedLeads_PreProductLeadFilter</x:v>
+      </x:c>
+      <x:c r="E22" s="26" t="str">
+        <x:v>Verify that the English Retail Admin user can access the My Closed Leads list view and that the Lead Sub Source filter is replaced with the Pre-Product Lead filter where applicable to Marketing leads.</x:v>
+      </x:c>
+      <x:c r="F22" s="26" t="str">
+        <x:v>Given Retail Admin is logged into RB as EN.
+When the user navigates to the Leads object.
+And the user opens the list view selector.
+And the user selects the "My Closed Leads" list view.
+And the user opens the Filters panel.</x:v>
+      </x:c>
+      <x:c r="G22" s="26" t="str">
+        <x:v>Then the "My Closed Leads" list view should load successfully and be accessible to the user.
+And the existing filter "Lead Sub Source not equal to PTYA" should be removed.
+And the new filter "Pre-Product Lead equals false" should be present for the applicable Marketing records.
+And the list view should display only records satisfying the updated filter criteria and all other existing filters.</x:v>
+      </x:c>
+      <x:c r="H22" s="26" t="str">
+        <x:v>User Coverage: English Retail Admin
+Shared With: English Business Admins Group
+Object: Leads
+List View: My Closed Leads
+List View API Name: My_Closed_Leads
+Record Type: Marketing (where applicable)
+Removed Filter: Lead Sub Source != PTYA
+New Filter: Pre-Product Lead = false</x:v>
+      </x:c>
+      <x:c r="I22" s="25" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="J22" s="25" t="str">
+        <x:v>Batman</x:v>
+      </x:c>
+      <x:c r="K22" s="25" t="str">
+        <x:v>HOJ</x:v>
+      </x:c>
+      <x:c r="L22" s="26" t="str"/>
+    </x:row>
+    <x:row r="23" ht="130" customHeight="1">
+      <x:c r="A23" s="25" t="str">
+        <x:v>TC-022</x:v>
+      </x:c>
+      <x:c r="B23" s="25" t="str">
+        <x:v>BIGBIRD-3029</x:v>
+      </x:c>
+      <x:c r="C23" s="27" t="str">
+        <x:v>EN</x:v>
+      </x:c>
+      <x:c r="D23" s="26" t="str">
+        <x:v>RetailRB_En_Admin_LeadsListView_LeadExceptions_PreProductLeadFilter</x:v>
+      </x:c>
+      <x:c r="E23" s="26" t="str">
+        <x:v>Verify that the English Retail Admin user can access the Lead Exceptions list view and that the Lead Sub Source filter is replaced with the Pre-Product Lead filter where applicable to Marketing leads.</x:v>
+      </x:c>
+      <x:c r="F23" s="26" t="str">
+        <x:v>Given Retail Admin is logged into RB as EN.
+When the user navigates to the Leads object.
+And the user opens the list view selector.
+And the user selects the "Lead Exceptions" list view.
+And the user opens the Filters panel.</x:v>
+      </x:c>
+      <x:c r="G23" s="26" t="str">
+        <x:v>Then the "Lead Exceptions" list view should load successfully and be accessible to the user.
+And the existing filter "Lead Sub Source not equal to PTYA" should be removed.
+And the new filter "Pre-Product Lead equals false" should be present for the applicable Marketing records.
+And the list view should display only records satisfying the updated filter criteria and all other existing filters.</x:v>
+      </x:c>
+      <x:c r="H23" s="26" t="str">
+        <x:v>User Coverage: English Retail Admin
+Shared With: English Business Admins Group
+Object: Leads
+List View: Lead Exceptions
+List View API Name: My_Relationships_General_Leads_Lead
+Record Type: Marketing (where applicable)
+Removed Filter: Lead Sub Source != PTYA
+New Filter: Pre-Product Lead = false</x:v>
+      </x:c>
+      <x:c r="I23" s="25" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="J23" s="25" t="str">
+        <x:v>Batman</x:v>
+      </x:c>
+      <x:c r="K23" s="25" t="str">
+        <x:v>HOJ</x:v>
+      </x:c>
+      <x:c r="L23" s="26" t="str"/>
+    </x:row>
+    <x:row r="24" ht="130" customHeight="1">
+      <x:c r="A24" s="25" t="str">
+        <x:v>TC-023</x:v>
+      </x:c>
+      <x:c r="B24" s="25" t="str">
+        <x:v>BIGBIRD-3029</x:v>
+      </x:c>
+      <x:c r="C24" s="27" t="str">
+        <x:v>EN</x:v>
+      </x:c>
+      <x:c r="D24" s="26" t="str">
+        <x:v>RetailRB_En_MarketingUser_LeadsListView_LeadExceptions_PreProductLeadFilter</x:v>
+      </x:c>
+      <x:c r="E24" s="26" t="str">
+        <x:v>Verify that the English Marketing User user can access the Lead Exceptions list view and that the Lead Sub Source filter is replaced with the Pre-Product Lead filter where applicable to Marketing leads.</x:v>
+      </x:c>
+      <x:c r="F24" s="26" t="str">
+        <x:v>Given Marketing User is logged into RB as EN.
+When the user navigates to the Leads object.
+And the user opens the list view selector.
+And the user selects the "Lead Exceptions" list view.
+And the user opens the Filters panel.</x:v>
+      </x:c>
+      <x:c r="G24" s="26" t="str">
+        <x:v>Then the "Lead Exceptions" list view should load successfully and be accessible to the user.
+And the existing filter "Lead Sub Source not equal to PTYA" should be removed.
+And the new filter "Pre-Product Lead equals false" should be present for the applicable Marketing records.
+And the list view should display only records satisfying the updated filter criteria and all other existing filters.</x:v>
+      </x:c>
+      <x:c r="H24" s="26" t="str">
+        <x:v>User Coverage: English Marketing User
+Shared With: English Marketing User Group
+Object: Leads
+List View: Lead Exceptions
+List View API Name: My_Relationships_General_Leads_Lead
+Record Type: Marketing (where applicable)
+Removed Filter: Lead Sub Source != PTYA
+New Filter: Pre-Product Lead = false</x:v>
+      </x:c>
+      <x:c r="I24" s="25" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="J24" s="25" t="str">
+        <x:v>Batman</x:v>
+      </x:c>
+      <x:c r="K24" s="25" t="str">
+        <x:v>HOJ</x:v>
+      </x:c>
+      <x:c r="L24" s="26" t="str"/>
+    </x:row>
+    <x:row r="25" ht="130" customHeight="1">
+      <x:c r="A25" s="25" t="str">
+        <x:v>TC-024</x:v>
+      </x:c>
+      <x:c r="B25" s="25" t="str">
+        <x:v>BIGBIRD-3029</x:v>
+      </x:c>
+      <x:c r="C25" s="27" t="str">
+        <x:v>EN</x:v>
+      </x:c>
+      <x:c r="D25" s="26" t="str">
+        <x:v>RetailRB_En_Admin_LeadsListView_ReferralExceptions_PreProductLeadFilter</x:v>
+      </x:c>
+      <x:c r="E25" s="26" t="str">
+        <x:v>Verify that the English Retail Admin user can access the Referral Exceptions list view and that the Lead Sub Source filter is replaced with the Pre-Product Lead filter where applicable to Marketing leads.</x:v>
+      </x:c>
+      <x:c r="F25" s="26" t="str">
+        <x:v>Given Retail Admin is logged into RB as EN.
+When the user navigates to the Leads object.
+And the user opens the list view selector.
+And the user selects the "Referral Exceptions" list view.
+And the user opens the Filters panel.</x:v>
+      </x:c>
+      <x:c r="G25" s="26" t="str">
+        <x:v>Then the "Referral Exceptions" list view should load successfully and be accessible to the user.
+And the existing filter "Lead Sub Source not equal to PTYA" should be removed.
+And the new filter "Pre-Product Lead equals false" should be present for the applicable Marketing records.
+And the list view should display only records satisfying the updated filter criteria and all other existing filters.</x:v>
+      </x:c>
+      <x:c r="H25" s="26" t="str">
+        <x:v>User Coverage: English Retail Admin
+Shared With: English Business Admins Group
+Object: Leads
+List View: Referral Exceptions
+List View API Name: My_Relationships_General_Referrals_Lead
+Record Type: Marketing (where applicable)
+Removed Filter: Lead Sub Source != PTYA
+New Filter: Pre-Product Lead = false</x:v>
+      </x:c>
+      <x:c r="I25" s="25" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="J25" s="25" t="str">
+        <x:v>Batman</x:v>
+      </x:c>
+      <x:c r="K25" s="25" t="str">
+        <x:v>HOJ</x:v>
+      </x:c>
+      <x:c r="L25" s="26" t="str"/>
+    </x:row>
+    <x:row r="26" ht="130" customHeight="1">
+      <x:c r="A26" s="25" t="str">
+        <x:v>TC-025</x:v>
+      </x:c>
+      <x:c r="B26" s="25" t="str">
+        <x:v>BIGBIRD-3029</x:v>
+      </x:c>
+      <x:c r="C26" s="27" t="str">
+        <x:v>EN</x:v>
+      </x:c>
+      <x:c r="D26" s="26" t="str">
+        <x:v>RetailRB_En_MarketingUser_LeadsListView_ReferralExceptions_PreProductLeadFilter</x:v>
+      </x:c>
+      <x:c r="E26" s="26" t="str">
+        <x:v>Verify that the English Marketing User user can access the Referral Exceptions list view and that the Lead Sub Source filter is replaced with the Pre-Product Lead filter where applicable to Marketing leads.</x:v>
+      </x:c>
+      <x:c r="F26" s="26" t="str">
+        <x:v>Given Marketing User is logged into RB as EN.
+When the user navigates to the Leads object.
+And the user opens the list view selector.
+And the user selects the "Referral Exceptions" list view.
+And the user opens the Filters panel.</x:v>
+      </x:c>
+      <x:c r="G26" s="26" t="str">
+        <x:v>Then the "Referral Exceptions" list view should load successfully and be accessible to the user.
+And the existing filter "Lead Sub Source not equal to PTYA" should be removed.
+And the new filter "Pre-Product Lead equals false" should be present for the applicable Marketing records.
+And the list view should display only records satisfying the updated filter criteria and all other existing filters.</x:v>
+      </x:c>
+      <x:c r="H26" s="26" t="str">
+        <x:v>User Coverage: English Marketing User
+Shared With: English Marketing User Group
+Object: Leads
+List View: Referral Exceptions
+List View API Name: My_Relationships_General_Referrals_Lead
+Record Type: Marketing (where applicable)
+Removed Filter: Lead Sub Source != PTYA
+New Filter: Pre-Product Lead = false</x:v>
+      </x:c>
+      <x:c r="I26" s="25" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="J26" s="25" t="str">
+        <x:v>Batman</x:v>
+      </x:c>
+      <x:c r="K26" s="25" t="str">
+        <x:v>HOJ</x:v>
+      </x:c>
+      <x:c r="L26" s="26" t="str"/>
+    </x:row>
+    <x:row r="27" ht="130" customHeight="1">
+      <x:c r="A27" s="25" t="str">
+        <x:v>TC-026</x:v>
+      </x:c>
+      <x:c r="B27" s="25" t="str">
+        <x:v>BIGBIRD-3029</x:v>
+      </x:c>
+      <x:c r="C27" s="27" t="str">
+        <x:v>EN</x:v>
+      </x:c>
+      <x:c r="D27" s="26" t="str">
+        <x:v>RetailRB_En_BM_LeadsListView_UnassignedReferrals_PreProductLeadFilter</x:v>
+      </x:c>
+      <x:c r="E27" s="26" t="str">
+        <x:v>Verify that the English Retail Manager user can access the Unassigned Referrals list view and that the Lead Sub Source filter is replaced with the Pre-Product Lead filter where applicable to Marketing leads.</x:v>
+      </x:c>
+      <x:c r="F27" s="26" t="str">
+        <x:v>Given Retail Manager is logged into RB as EN.
+When the user navigates to the Leads object.
+And the user opens the list view selector.
+And the user selects the "Unassigned Referrals" list view.
+And the user opens the Filters panel.</x:v>
+      </x:c>
+      <x:c r="G27" s="26" t="str">
+        <x:v>Then the "Unassigned Referrals" list view should load successfully and be accessible to the user.
+And the existing filter "Lead Sub Source not equal to PTYA" should be removed.
+And the new filter "Pre-Product Lead equals false" should be present for the applicable Marketing records.
+And the list view should display only records satisfying the updated filter criteria and all other existing filters.</x:v>
+      </x:c>
+      <x:c r="H27" s="26" t="str">
+        <x:v>User Coverage: English Retail Manager
+Shared With: English Branch Manager Users Group
+Object: Leads
+List View: Unassigned Referrals
+List View API Name: My_Relationships_Unassigned_Referrals_Lead
+Record Type: Marketing (where applicable)
+Removed Filter: Lead Sub Source != PTYA
+New Filter: Pre-Product Lead = false</x:v>
+      </x:c>
+      <x:c r="I27" s="25" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="J27" s="25" t="str">
+        <x:v>Batman</x:v>
+      </x:c>
+      <x:c r="K27" s="25" t="str">
+        <x:v>HOJ</x:v>
+      </x:c>
+      <x:c r="L27" s="26" t="str"/>
+    </x:row>
+    <x:row r="28" ht="130" customHeight="1">
+      <x:c r="A28" s="25" t="str">
+        <x:v>TC-027</x:v>
+      </x:c>
+      <x:c r="B28" s="25" t="str">
+        <x:v>BIGBIRD-3029</x:v>
+      </x:c>
+      <x:c r="C28" s="27" t="str">
+        <x:v>EN</x:v>
+      </x:c>
+      <x:c r="D28" s="26" t="str">
+        <x:v>RetailRB_En_Admin_LeadsListView_UnassignedReferrals_PreProductLeadFilter</x:v>
+      </x:c>
+      <x:c r="E28" s="26" t="str">
+        <x:v>Verify that the English Retail Admin user can access the Unassigned Referrals list view and that the Lead Sub Source filter is replaced with the Pre-Product Lead filter where applicable to Marketing leads.</x:v>
+      </x:c>
+      <x:c r="F28" s="26" t="str">
+        <x:v>Given Retail Admin is logged into RB as EN.
+When the user navigates to the Leads object.
+And the user opens the list view selector.
+And the user selects the "Unassigned Referrals" list view.
+And the user opens the Filters panel.</x:v>
+      </x:c>
+      <x:c r="G28" s="26" t="str">
+        <x:v>Then the "Unassigned Referrals" list view should load successfully and be accessible to the user.
+And the existing filter "Lead Sub Source not equal to PTYA" should be removed.
+And the new filter "Pre-Product Lead equals false" should be present for the applicable Marketing records.
+And the list view should display only records satisfying the updated filter criteria and all other existing filters.</x:v>
+      </x:c>
+      <x:c r="H28" s="26" t="str">
+        <x:v>User Coverage: English Retail Admin
+Shared With: English Business Admins Group
+Object: Leads
+List View: Unassigned Referrals
+List View API Name: My_Relationships_Unassigned_Referrals_Lead
+Record Type: Marketing (where applicable)
+Removed Filter: Lead Sub Source != PTYA
+New Filter: Pre-Product Lead = false</x:v>
+      </x:c>
+      <x:c r="I28" s="25" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="J28" s="25" t="str">
+        <x:v>Batman</x:v>
+      </x:c>
+      <x:c r="K28" s="25" t="str">
+        <x:v>HOJ</x:v>
+      </x:c>
+      <x:c r="L28" s="26" t="str"/>
+    </x:row>
+    <x:row r="29" ht="130" customHeight="1">
+      <x:c r="A29" s="25" t="str">
+        <x:v>TC-028</x:v>
+      </x:c>
+      <x:c r="B29" s="25" t="str">
+        <x:v>BIGBIRD-3029</x:v>
+      </x:c>
+      <x:c r="C29" s="27" t="str">
+        <x:v>EN</x:v>
+      </x:c>
+      <x:c r="D29" s="26" t="str">
+        <x:v>MMSRB_En_AVP_LeadsListView_MyTeamsBranchReferrals_PreProductLeadFilter</x:v>
+      </x:c>
+      <x:c r="E29" s="26" t="str">
+        <x:v>Verify that the English MMS AVP user can access the My Team's Branch Referrals list view and that the Lead Sub Source filter is replaced with the Pre-Product Lead filter where applicable to Marketing leads.</x:v>
+      </x:c>
+      <x:c r="F29" s="26" t="str">
+        <x:v>Given MMS AVP is logged into RB as EN.
+When the user navigates to the Leads object.
+And the user opens the list view selector.
+And the user selects the "My Team's Branch Referrals" list view.
+And the user opens the Filters panel.</x:v>
+      </x:c>
+      <x:c r="G29" s="26" t="str">
+        <x:v>Then the "My Team's Branch Referrals" list view should load successfully and be accessible to the user.
+And the existing filter "Lead Sub Source not equal to PTYA" should be removed.
+And the new filter "Pre-Product Lead equals false" should be present for the applicable Marketing records.
+And the list view should display only records satisfying the updated filter criteria and all other existing filters.</x:v>
+      </x:c>
+      <x:c r="H29" s="26" t="str">
+        <x:v>User Coverage: English MMS AVP
+Shared With: English AVP Users Group
+Object: Leads
+List View: My Team's Branch Referrals
+List View API Name: My_Team_s_Branch_Referrals
+Record Type: Marketing (where applicable)
+Removed Filter: Lead Sub Source != PTYA
+New Filter: Pre-Product Lead = false</x:v>
+      </x:c>
+      <x:c r="I29" s="25" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="J29" s="25" t="str">
+        <x:v>Batman</x:v>
+      </x:c>
+      <x:c r="K29" s="25" t="str">
+        <x:v>HOJ</x:v>
+      </x:c>
+      <x:c r="L29" s="26" t="str"/>
+    </x:row>
+    <x:row r="30" ht="130" customHeight="1">
+      <x:c r="A30" s="25" t="str">
+        <x:v>TC-029</x:v>
+      </x:c>
+      <x:c r="B30" s="25" t="str">
+        <x:v>BIGBIRD-3029</x:v>
+      </x:c>
+      <x:c r="C30" s="27" t="str">
+        <x:v>EN</x:v>
+      </x:c>
+      <x:c r="D30" s="26" t="str">
+        <x:v>MMSRB_En_DM_LeadsListView_MyTeamsBranchReferrals_PreProductLeadFilter</x:v>
+      </x:c>
+      <x:c r="E30" s="26" t="str">
+        <x:v>Verify that the English MMS District Manager user can access the My Team's Branch Referrals list view and that the Lead Sub Source filter is replaced with the Pre-Product Lead filter where applicable to Marketing leads.</x:v>
+      </x:c>
+      <x:c r="F30" s="26" t="str">
+        <x:v>Given MMS District Manager is logged into RB as EN.
+When the user navigates to the Leads object.
+And the user opens the list view selector.
+And the user selects the "My Team's Branch Referrals" list view.
+And the user opens the Filters panel.</x:v>
+      </x:c>
+      <x:c r="G30" s="26" t="str">
+        <x:v>Then the "My Team's Branch Referrals" list view should load successfully and be accessible to the user.
+And the existing filter "Lead Sub Source not equal to PTYA" should be removed.
+And the new filter "Pre-Product Lead equals false" should be present for the applicable Marketing records.
+And the list view should display only records satisfying the updated filter criteria and all other existing filters.</x:v>
+      </x:c>
+      <x:c r="H30" s="26" t="str">
+        <x:v>User Coverage: English MMS District Manager
+Shared With: English SM Users Group
+Object: Leads
+List View: My Team's Branch Referrals
+List View API Name: My_Team_s_Branch_Referrals
+Record Type: Marketing (where applicable)
+Removed Filter: Lead Sub Source != PTYA
+New Filter: Pre-Product Lead = false</x:v>
+      </x:c>
+      <x:c r="I30" s="25" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="J30" s="25" t="str">
+        <x:v>Batman</x:v>
+      </x:c>
+      <x:c r="K30" s="25" t="str">
+        <x:v>HOJ</x:v>
+      </x:c>
+      <x:c r="L30" s="26" t="str"/>
+    </x:row>
+    <x:row r="31" ht="130" customHeight="1">
+      <x:c r="A31" s="25" t="str">
+        <x:v>TC-030</x:v>
+      </x:c>
+      <x:c r="B31" s="25" t="str">
+        <x:v>BIGBIRD-3029</x:v>
+      </x:c>
+      <x:c r="C31" s="27" t="str">
+        <x:v>EN</x:v>
+      </x:c>
+      <x:c r="D31" s="26" t="str">
+        <x:v>RSGRB_En_TL_LeadsListView_MyTeamsSelfGeneratedLeads_PreProductLeadFilter</x:v>
+      </x:c>
+      <x:c r="E31" s="26" t="str">
+        <x:v>Verify that the English RSG Team Leader user can access the My Team's Self Generated Leads list view and that the Lead Sub Source filter is replaced with the Pre-Product Lead filter where applicable to Marketing leads.</x:v>
+      </x:c>
+      <x:c r="F31" s="26" t="str">
+        <x:v>Given RSG Team Leader is logged into RB as EN.
+When the user navigates to the Leads object.
+And the user opens the list view selector.
+And the user selects the "My Team's Self Generated Leads" list view.
+And the user opens the Filters panel.</x:v>
+      </x:c>
+      <x:c r="G31" s="26" t="str">
+        <x:v>Then the "My Team's Self Generated Leads" list view should load successfully and be accessible to the user.
+And the existing filter "Lead Sub Source not equal to PTYA" should be removed.
+And the new filter "Pre-Product Lead equals false" should be present for the applicable Marketing records.
+And the list view should display only records satisfying the updated filter criteria and all other existing filters.</x:v>
+      </x:c>
+      <x:c r="H31" s="26" t="str">
+        <x:v>User Coverage: English RSG Team Leader
+Shared With: English PCMR Manager Users Group
+Object: Leads
+List View: My Team's Self Generated Leads
+List View API Name: My_Team_s_Self_Generated_Leads
+Record Type: Marketing (where applicable)
+Removed Filter: Lead Sub Source != PTYA
+New Filter: Pre-Product Lead = false</x:v>
+      </x:c>
+      <x:c r="I31" s="25" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="J31" s="25" t="str">
+        <x:v>Batman</x:v>
+      </x:c>
+      <x:c r="K31" s="25" t="str">
+        <x:v>HOJ</x:v>
+      </x:c>
+      <x:c r="L31" s="26" t="str"/>
+    </x:row>
+    <x:row r="32" ht="130" customHeight="1">
+      <x:c r="A32" s="25" t="str">
+        <x:v>TC-031</x:v>
+      </x:c>
+      <x:c r="B32" s="25" t="str">
+        <x:v>BIGBIRD-3029</x:v>
+      </x:c>
+      <x:c r="C32" s="27" t="str">
+        <x:v>FR</x:v>
+      </x:c>
+      <x:c r="D32" s="26" t="str">
+        <x:v>RSGRB_Fr_TL_LeadsListView_PistesCreesParMonEquipe_PreProductLeadFilter</x:v>
+      </x:c>
+      <x:c r="E32" s="26" t="str">
+        <x:v>Verify that the French RSG Team Leader user can access the Pistes créées par mon équipe list view and that the Lead Sub Source filter is replaced with the Pre-Product Lead filter where applicable to Marketing leads.</x:v>
+      </x:c>
+      <x:c r="F32" s="26" t="str">
+        <x:v>Given RSG Team Leader is logged into RB as FR.
+When the user navigates to the Leads object.
+And the user opens the list view selector.
+And the user selects the "Pistes créées par mon équipe" list view.
+And the user opens the Filters panel.</x:v>
+      </x:c>
+      <x:c r="G32" s="26" t="str">
+        <x:v>Then the "Pistes créées par mon équipe" list view should load successfully and be accessible to the user.
+And the existing filter "Lead Sub Source not equal to PTYA" should be removed.
+And the new filter "Pre-Product Lead equals false" should be present for the applicable Marketing records.
+And the list view should display only records satisfying the updated filter criteria and all other existing filters.</x:v>
+      </x:c>
+      <x:c r="H32" s="26" t="str">
+        <x:v>User Coverage: French RSG Team Leader
+Shared With: French PCMR Manager Users Group
+Object: Leads
+List View: Pistes créées par mon équipe
+List View API Name: Pistes_cr_es_par_mon_quipe
+Record Type: Marketing (where applicable)
+Removed Filter: Lead Sub Source != PTYA
+New Filter: Pre-Product Lead = false</x:v>
+      </x:c>
+      <x:c r="I32" s="25" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="J32" s="25" t="str">
+        <x:v>Batman</x:v>
+      </x:c>
+      <x:c r="K32" s="25" t="str">
+        <x:v>HOJ</x:v>
+      </x:c>
+      <x:c r="L32" s="26" t="str"/>
+    </x:row>
+    <x:row r="33" ht="130" customHeight="1">
+      <x:c r="A33" s="25" t="str">
+        <x:v>TC-032</x:v>
+      </x:c>
+      <x:c r="B33" s="25" t="str">
+        <x:v>BIGBIRD-3029</x:v>
+      </x:c>
+      <x:c r="C33" s="27" t="str">
+        <x:v>FR</x:v>
+      </x:c>
+      <x:c r="D33" s="26" t="str">
+        <x:v>RetailRB_Fr_BM_LeadsListView_PistesDeLaSuccursale_PreProductLeadFilter</x:v>
+      </x:c>
+      <x:c r="E33" s="26" t="str">
+        <x:v>Verify that the French Retail Manager user can access the Pistes de la succursale list view and that the Lead Sub Source filter is replaced with the Pre-Product Lead filter where applicable to Marketing leads.</x:v>
+      </x:c>
+      <x:c r="F33" s="26" t="str">
+        <x:v>Given Retail Manager is logged into RB as FR.
+When the user navigates to the Leads object.
+And the user opens the list view selector.
+And the user selects the "Pistes de la succursale" list view.
+And the user opens the Filters panel.</x:v>
+      </x:c>
+      <x:c r="G33" s="26" t="str">
+        <x:v>Then the "Pistes de la succursale" list view should load successfully and be accessible to the user.
+And the existing filter "Lead Sub Source not equal to PTYA" should be removed.
+And the new filter "Pre-Product Lead equals false" should be present for the applicable Marketing records.
+And the list view should display only records satisfying the updated filter criteria and all other existing filters.</x:v>
+      </x:c>
+      <x:c r="H33" s="26" t="str">
+        <x:v>User Coverage: French Retail Manager
+Shared With: French Branch Manager Users Group
+Object: Leads
+List View: Pistes de la succursale
+List View API Name: Pistes_de_la_succursale
+Record Type: Marketing (where applicable)
+Removed Filter: Lead Sub Source != PTYA
+New Filter: Pre-Product Lead = false</x:v>
+      </x:c>
+      <x:c r="I33" s="25" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="J33" s="25" t="str">
+        <x:v>Batman</x:v>
+      </x:c>
+      <x:c r="K33" s="25" t="str">
+        <x:v>HOJ</x:v>
+      </x:c>
+      <x:c r="L33" s="26" t="str"/>
+    </x:row>
+    <x:row r="34" ht="130" customHeight="1">
+      <x:c r="A34" s="25" t="str">
+        <x:v>TC-033</x:v>
+      </x:c>
+      <x:c r="B34" s="25" t="str">
+        <x:v>BIGBIRD-3029</x:v>
+      </x:c>
+      <x:c r="C34" s="27" t="str">
+        <x:v>FR</x:v>
+      </x:c>
+      <x:c r="D34" s="26" t="str">
+        <x:v>RetailRB_Fr_Admin_LeadsListView_PistesDeLaSuccursale_PreProductLeadFilter</x:v>
+      </x:c>
+      <x:c r="E34" s="26" t="str">
+        <x:v>Verify that the French Retail Admin user can access the Pistes de la succursale list view and that the Lead Sub Source filter is replaced with the Pre-Product Lead filter where applicable to Marketing leads.</x:v>
+      </x:c>
+      <x:c r="F34" s="26" t="str">
+        <x:v>Given Retail Admin is logged into RB as FR.
+When the user navigates to the Leads object.
+And the user opens the list view selector.
+And the user selects the "Pistes de la succursale" list view.
+And the user opens the Filters panel.</x:v>
+      </x:c>
+      <x:c r="G34" s="26" t="str">
+        <x:v>Then the "Pistes de la succursale" list view should load successfully and be accessible to the user.
+And the existing filter "Lead Sub Source not equal to PTYA" should be removed.
+And the new filter "Pre-Product Lead equals false" should be present for the applicable Marketing records.
+And the list view should display only records satisfying the updated filter criteria and all other existing filters.</x:v>
+      </x:c>
+      <x:c r="H34" s="26" t="str">
+        <x:v>User Coverage: French Retail Admin
+Shared With: French Business Admins Group
+Object: Leads
+List View: Pistes de la succursale
+List View API Name: Pistes_de_la_succursale
+Record Type: Marketing (where applicable)
+Removed Filter: Lead Sub Source != PTYA
+New Filter: Pre-Product Lead = false</x:v>
+      </x:c>
+      <x:c r="I34" s="25" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="J34" s="25" t="str">
+        <x:v>Batman</x:v>
+      </x:c>
+      <x:c r="K34" s="25" t="str">
+        <x:v>HOJ</x:v>
+      </x:c>
+      <x:c r="L34" s="26" t="str"/>
+    </x:row>
+    <x:row r="35" ht="130" customHeight="1">
+      <x:c r="A35" s="25" t="str">
+        <x:v>TC-034</x:v>
+      </x:c>
+      <x:c r="B35" s="25" t="str">
+        <x:v>BIGBIRD-3029</x:v>
+      </x:c>
+      <x:c r="C35" s="27" t="str">
+        <x:v>FR</x:v>
+      </x:c>
+      <x:c r="D35" s="26" t="str">
+        <x:v>RetailRB_Fr_BM_LeadsListView_PistesFermeesDeLaSuccursale_PreProductLeadFilter</x:v>
+      </x:c>
+      <x:c r="E35" s="26" t="str">
+        <x:v>Verify that the French Retail Manager user can access the Pistes fermées de la succursale list view and that the Lead Sub Source filter is replaced with the Pre-Product Lead filter where applicable to Marketing leads.</x:v>
+      </x:c>
+      <x:c r="F35" s="26" t="str">
+        <x:v>Given Retail Manager is logged into RB as FR.
+When the user navigates to the Leads object.
+And the user opens the list view selector.
+And the user selects the "Pistes fermées de la succursale" list view.
+And the user opens the Filters panel.</x:v>
+      </x:c>
+      <x:c r="G35" s="26" t="str">
+        <x:v>Then the "Pistes fermées de la succursale" list view should load successfully and be accessible to the user.
+And the existing filter "Lead Sub Source not equal to PTYA" should be removed.
+And the new filter "Pre-Product Lead equals false" should be present for the applicable Marketing records.
+And the list view should display only records satisfying the updated filter criteria and all other existing filters.</x:v>
+      </x:c>
+      <x:c r="H35" s="26" t="str">
+        <x:v>User Coverage: French Retail Manager
+Shared With: French Branch Manager Users Group
+Object: Leads
+List View: Pistes fermées de la succursale
+List View API Name: Pistes_ferm_es_de_la_succursale
+Record Type: Marketing (where applicable)
+Removed Filter: Lead Sub Source != PTYA
+New Filter: Pre-Product Lead = false</x:v>
+      </x:c>
+      <x:c r="I35" s="25" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="J35" s="25" t="str">
+        <x:v>Batman</x:v>
+      </x:c>
+      <x:c r="K35" s="25" t="str">
+        <x:v>HOJ</x:v>
+      </x:c>
+      <x:c r="L35" s="26" t="str"/>
+    </x:row>
+    <x:row r="36" ht="130" customHeight="1">
+      <x:c r="A36" s="25" t="str">
+        <x:v>TC-035</x:v>
+      </x:c>
+      <x:c r="B36" s="25" t="str">
+        <x:v>BIGBIRD-3029</x:v>
+      </x:c>
+      <x:c r="C36" s="27" t="str">
+        <x:v>FR</x:v>
+      </x:c>
+      <x:c r="D36" s="26" t="str">
+        <x:v>RetailRB_Fr_Admin_LeadsListView_PistesFermeesDeLaSuccursale_PreProductLeadFilter</x:v>
+      </x:c>
+      <x:c r="E36" s="26" t="str">
+        <x:v>Verify that the French Retail Admin user can access the Pistes fermées de la succursale list view and that the Lead Sub Source filter is replaced with the Pre-Product Lead filter where applicable to Marketing leads.</x:v>
+      </x:c>
+      <x:c r="F36" s="26" t="str">
+        <x:v>Given Retail Admin is logged into RB as FR.
+When the user navigates to the Leads object.
+And the user opens the list view selector.
+And the user selects the "Pistes fermées de la succursale" list view.
+And the user opens the Filters panel.</x:v>
+      </x:c>
+      <x:c r="G36" s="26" t="str">
+        <x:v>Then the "Pistes fermées de la succursale" list view should load successfully and be accessible to the user.
+And the existing filter "Lead Sub Source not equal to PTYA" should be removed.
+And the new filter "Pre-Product Lead equals false" should be present for the applicable Marketing records.
+And the list view should display only records satisfying the updated filter criteria and all other existing filters.</x:v>
+      </x:c>
+      <x:c r="H36" s="26" t="str">
+        <x:v>User Coverage: French Retail Admin
+Shared With: French Business Admins Group
+Object: Leads
+List View: Pistes fermées de la succursale
+List View API Name: Pistes_ferm_es_de_la_succursale
+Record Type: Marketing (where applicable)
+Removed Filter: Lead Sub Source != PTYA
+New Filter: Pre-Product Lead = false</x:v>
+      </x:c>
+      <x:c r="I36" s="25" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="J36" s="25" t="str">
+        <x:v>Batman</x:v>
+      </x:c>
+      <x:c r="K36" s="25" t="str">
+        <x:v>HOJ</x:v>
+      </x:c>
+      <x:c r="L36" s="26" t="str"/>
+    </x:row>
+    <x:row r="37" ht="130" customHeight="1">
+      <x:c r="A37" s="25" t="str">
+        <x:v>TC-036</x:v>
+      </x:c>
+      <x:c r="B37" s="25" t="str">
+        <x:v>BIGBIRD-3029</x:v>
+      </x:c>
+      <x:c r="C37" s="27" t="str">
+        <x:v>FR</x:v>
+      </x:c>
+      <x:c r="D37" s="26" t="str">
+        <x:v>RetailRB_Fr_BM_LeadsListView_PistesNonAttribuees_PreProductLeadFilter</x:v>
+      </x:c>
+      <x:c r="E37" s="26" t="str">
+        <x:v>Verify that the French Retail Manager user can access the Pistes non attribuées list view and that the Lead Sub Source filter is replaced with the Pre-Product Lead filter where applicable to Marketing leads.</x:v>
+      </x:c>
+      <x:c r="F37" s="26" t="str">
+        <x:v>Given Retail Manager is logged into RB as FR.
+When the user navigates to the Leads object.
+And the user opens the list view selector.
+And the user selects the "Pistes non attribuées" list view.
+And the user opens the Filters panel.</x:v>
+      </x:c>
+      <x:c r="G37" s="26" t="str">
+        <x:v>Then the "Pistes non attribuées" list view should load successfully and be accessible to the user.
+And the existing filter "Lead Sub Source not equal to PTYA" should be removed.
+And the new filter "Pre-Product Lead equals false" should be present for the applicable Marketing records.
+And the list view should display only records satisfying the updated filter criteria and all other existing filters.</x:v>
+      </x:c>
+      <x:c r="H37" s="26" t="str">
+        <x:v>User Coverage: French Retail Manager
+Shared With: French Branch Manager Users Group
+Object: Leads
+List View: Pistes non attribuées
+List View API Name: Pistes_non_attribu_es
+Record Type: Marketing (where applicable)
+Removed Filter: Lead Sub Source != PTYA
+New Filter: Pre-Product Lead = false</x:v>
+      </x:c>
+      <x:c r="I37" s="25" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="J37" s="25" t="str">
+        <x:v>Batman</x:v>
+      </x:c>
+      <x:c r="K37" s="25" t="str">
+        <x:v>HOJ</x:v>
+      </x:c>
+      <x:c r="L37" s="26" t="str"/>
+    </x:row>
+    <x:row r="38" ht="130" customHeight="1">
+      <x:c r="A38" s="25" t="str">
+        <x:v>TC-037</x:v>
+      </x:c>
+      <x:c r="B38" s="25" t="str">
+        <x:v>BIGBIRD-3029</x:v>
+      </x:c>
+      <x:c r="C38" s="27" t="str">
+        <x:v>FR</x:v>
+      </x:c>
+      <x:c r="D38" s="26" t="str">
+        <x:v>RetailRB_Fr_Admin_LeadsListView_PistesNonAttribuees_PreProductLeadFilter</x:v>
+      </x:c>
+      <x:c r="E38" s="26" t="str">
+        <x:v>Verify that the French Retail Admin user can access the Pistes non attribuées list view and that the Lead Sub Source filter is replaced with the Pre-Product Lead filter where applicable to Marketing leads.</x:v>
+      </x:c>
+      <x:c r="F38" s="26" t="str">
+        <x:v>Given Retail Admin is logged into RB as FR.
+When the user navigates to the Leads object.
+And the user opens the list view selector.
+And the user selects the "Pistes non attribuées" list view.
+And the user opens the Filters panel.</x:v>
+      </x:c>
+      <x:c r="G38" s="26" t="str">
+        <x:v>Then the "Pistes non attribuées" list view should load successfully and be accessible to the user.
+And the existing filter "Lead Sub Source not equal to PTYA" should be removed.
+And the new filter "Pre-Product Lead equals false" should be present for the applicable Marketing records.
+And the list view should display only records satisfying the updated filter criteria and all other existing filters.</x:v>
+      </x:c>
+      <x:c r="H38" s="26" t="str">
+        <x:v>User Coverage: French Retail Admin
+Shared With: French Business Admins Group
+Object: Leads
+List View: Pistes non attribuées
+List View API Name: Pistes_non_attribu_es
+Record Type: Marketing (where applicable)
+Removed Filter: Lead Sub Source != PTYA
+New Filter: Pre-Product Lead = false</x:v>
+      </x:c>
+      <x:c r="I38" s="25" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="J38" s="25" t="str">
+        <x:v>Batman</x:v>
+      </x:c>
+      <x:c r="K38" s="25" t="str">
+        <x:v>HOJ</x:v>
+      </x:c>
+      <x:c r="L38" s="26" t="str"/>
+    </x:row>
+    <x:row r="39" ht="130" customHeight="1">
+      <x:c r="A39" s="25" t="str">
+        <x:v>TC-038</x:v>
+      </x:c>
+      <x:c r="B39" s="25" t="str">
+        <x:v>BIGBIRD-3029</x:v>
+      </x:c>
+      <x:c r="C39" s="27" t="str">
+        <x:v>FR</x:v>
+      </x:c>
+      <x:c r="D39" s="26" t="str">
+        <x:v>RetailRB_Fr_BM_LeadsListView_RecommandationsNonAttribuees_PreProductLeadFilter</x:v>
+      </x:c>
+      <x:c r="E39" s="26" t="str">
+        <x:v>Verify that the French Retail Manager user can access the Recommandations non attribuées list view and that the Lead Sub Source filter is replaced with the Pre-Product Lead filter where applicable to Marketing leads.</x:v>
+      </x:c>
+      <x:c r="F39" s="26" t="str">
+        <x:v>Given Retail Manager is logged into RB as FR.
+When the user navigates to the Leads object.
+And the user opens the list view selector.
+And the user selects the "Recommandations non attribuées" list view.
+And the user opens the Filters panel.</x:v>
+      </x:c>
+      <x:c r="G39" s="26" t="str">
+        <x:v>Then the "Recommandations non attribuées" list view should load successfully and be accessible to the user.
+And the existing filter "Lead Sub Source not equal to PTYA" should be removed.
+And the new filter "Pre-Product Lead equals false" should be present for the applicable Marketing records.
+And the list view should display only records satisfying the updated filter criteria and all other existing filters.</x:v>
+      </x:c>
+      <x:c r="H39" s="26" t="str">
+        <x:v>User Coverage: French Retail Manager
+Shared With: French Branch Manager Users Group
+Object: Leads
+List View: Recommandations non attribuées
+List View API Name: Recommandations_non_attribu_es
+Record Type: Marketing (where applicable)
+Removed Filter: Lead Sub Source != PTYA
+New Filter: Pre-Product Lead = false</x:v>
+      </x:c>
+      <x:c r="I39" s="25" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="J39" s="25" t="str">
+        <x:v>Batman</x:v>
+      </x:c>
+      <x:c r="K39" s="25" t="str">
+        <x:v>HOJ</x:v>
+      </x:c>
+      <x:c r="L39" s="26" t="str"/>
+    </x:row>
+    <x:row r="40" ht="130" customHeight="1">
+      <x:c r="A40" s="25" t="str">
+        <x:v>TC-039</x:v>
+      </x:c>
+      <x:c r="B40" s="25" t="str">
+        <x:v>BIGBIRD-3029</x:v>
+      </x:c>
+      <x:c r="C40" s="27" t="str">
+        <x:v>FR</x:v>
+      </x:c>
+      <x:c r="D40" s="26" t="str">
+        <x:v>RetailRB_Fr_Admin_LeadsListView_RecommandationsNonAttribuees_PreProductLeadFilter</x:v>
+      </x:c>
+      <x:c r="E40" s="26" t="str">
+        <x:v>Verify that the French Retail Admin user can access the Recommandations non attribuées list view and that the Lead Sub Source filter is replaced with the Pre-Product Lead filter where applicable to Marketing leads.</x:v>
+      </x:c>
+      <x:c r="F40" s="26" t="str">
+        <x:v>Given Retail Admin is logged into RB as FR.
+When the user navigates to the Leads object.
+And the user opens the list view selector.
+And the user selects the "Recommandations non attribuées" list view.
+And the user opens the Filters panel.</x:v>
+      </x:c>
+      <x:c r="G40" s="26" t="str">
+        <x:v>Then the "Recommandations non attribuées" list view should load successfully and be accessible to the user.
+And the existing filter "Lead Sub Source not equal to PTYA" should be removed.
+And the new filter "Pre-Product Lead equals false" should be present for the applicable Marketing records.
+And the list view should display only records satisfying the updated filter criteria and all other existing filters.</x:v>
+      </x:c>
+      <x:c r="H40" s="26" t="str">
+        <x:v>User Coverage: French Retail Admin
+Shared With: French Business Admins Group
+Object: Leads
+List View: Recommandations non attribuées
+List View API Name: Recommandations_non_attribu_es
+Record Type: Marketing (where applicable)
+Removed Filter: Lead Sub Source != PTYA
+New Filter: Pre-Product Lead = false</x:v>
+      </x:c>
+      <x:c r="I40" s="25" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="J40" s="25" t="str">
+        <x:v>Batman</x:v>
+      </x:c>
+      <x:c r="K40" s="25" t="str">
+        <x:v>HOJ</x:v>
+      </x:c>
+      <x:c r="L40" s="26" t="str"/>
+    </x:row>
+    <x:row r="41" ht="130" customHeight="1">
+      <x:c r="A41" s="25" t="str">
+        <x:v>TC-040</x:v>
+      </x:c>
+      <x:c r="B41" s="25" t="str">
+        <x:v>BIGBIRD-3029</x:v>
+      </x:c>
+      <x:c r="C41" s="27" t="str">
+        <x:v>FR</x:v>
+      </x:c>
+      <x:c r="D41" s="26" t="str">
+        <x:v>MMSRB_Fr_AVP_LeadsListView_ToutesLesPistes_PreProductLeadFilter</x:v>
+      </x:c>
+      <x:c r="E41" s="26" t="str">
+        <x:v>Verify that the French MMS AVP user can access the Toutes les pistes list view and that the Lead Sub Source filter is replaced with the Pre-Product Lead filter where applicable to Marketing leads.</x:v>
+      </x:c>
+      <x:c r="F41" s="26" t="str">
+        <x:v>Given MMS AVP is logged into RB as FR.
+When the user navigates to the Leads object.
+And the user opens the list view selector.
+And the user selects the "Toutes les pistes" list view.
+And the user opens the Filters panel.</x:v>
+      </x:c>
+      <x:c r="G41" s="26" t="str">
+        <x:v>Then the "Toutes les pistes" list view should load successfully and be accessible to the user.
+And the existing filter "Lead Sub Source not equal to PTYA" should be removed.
+And the new filter "Pre-Product Lead equals false" should be present for the applicable Marketing records.
+And the list view should display only records satisfying the updated filter criteria and all other existing filters.</x:v>
+      </x:c>
+      <x:c r="H41" s="26" t="str">
+        <x:v>User Coverage: French MMS AVP
+Shared With: French AVP Users Group
+Object: Leads
+List View: Toutes les pistes
+List View API Name: Toutes_les_pistes
+Record Type: Marketing (where applicable)
+Removed Filter: Lead Sub Source != PTYA
+New Filter: Pre-Product Lead = false</x:v>
+      </x:c>
+      <x:c r="I41" s="25" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="J41" s="25" t="str">
+        <x:v>Batman</x:v>
+      </x:c>
+      <x:c r="K41" s="25" t="str">
+        <x:v>HOJ</x:v>
+      </x:c>
+      <x:c r="L41" s="26" t="str"/>
+    </x:row>
+    <x:row r="42" ht="130" customHeight="1">
+      <x:c r="A42" s="25" t="str">
+        <x:v>TC-041</x:v>
+      </x:c>
+      <x:c r="B42" s="25" t="str">
+        <x:v>BIGBIRD-3029</x:v>
+      </x:c>
+      <x:c r="C42" s="27" t="str">
+        <x:v>FR</x:v>
+      </x:c>
+      <x:c r="D42" s="26" t="str">
+        <x:v>MMSRB_Fr_Field_LeadsListView_ToutesLesPistes_PreProductLeadFilter</x:v>
+      </x:c>
+      <x:c r="E42" s="26" t="str">
+        <x:v>Verify that the French MMS Field user can access the Toutes les pistes list view and that the Lead Sub Source filter is replaced with the Pre-Product Lead filter where applicable to Marketing leads.</x:v>
+      </x:c>
+      <x:c r="F42" s="26" t="str">
+        <x:v>Given MMS Field is logged into RB as FR.
+When the user navigates to the Leads object.
+And the user opens the list view selector.
+And the user selects the "Toutes les pistes" list view.
+And the user opens the Filters panel.</x:v>
+      </x:c>
+      <x:c r="G42" s="26" t="str">
+        <x:v>Then the "Toutes les pistes" list view should load successfully and be accessible to the user.
+And the existing filter "Lead Sub Source not equal to PTYA" should be removed.
+And the new filter "Pre-Product Lead equals false" should be present for the applicable Marketing records.
+And the list view should display only records satisfying the updated filter criteria and all other existing filters.</x:v>
+      </x:c>
+      <x:c r="H42" s="26" t="str">
+        <x:v>User Coverage: French MMS Field
+Shared With: French MMS Users Group
+Object: Leads
+List View: Toutes les pistes
+List View API Name: Toutes_les_pistes
+Record Type: Marketing (where applicable)
+Removed Filter: Lead Sub Source != PTYA
+New Filter: Pre-Product Lead = false</x:v>
+      </x:c>
+      <x:c r="I42" s="25" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="J42" s="25" t="str">
+        <x:v>Batman</x:v>
+      </x:c>
+      <x:c r="K42" s="25" t="str">
+        <x:v>HOJ</x:v>
+      </x:c>
+      <x:c r="L42" s="26" t="str"/>
+    </x:row>
+    <x:row r="43" ht="130" customHeight="1">
+      <x:c r="A43" s="25" t="str">
+        <x:v>TC-042</x:v>
+      </x:c>
+      <x:c r="B43" s="25" t="str">
+        <x:v>BIGBIRD-3029</x:v>
+      </x:c>
+      <x:c r="C43" s="27" t="str">
+        <x:v>FR</x:v>
+      </x:c>
+      <x:c r="D43" s="26" t="str">
+        <x:v>MMSARB_Fr_Field_LeadsListView_ToutesLesPistes_PreProductLeadFilter</x:v>
+      </x:c>
+      <x:c r="E43" s="26" t="str">
+        <x:v>Verify that the French MMSA Field user can access the Toutes les pistes list view and that the Lead Sub Source filter is replaced with the Pre-Product Lead filter where applicable to Marketing leads.</x:v>
+      </x:c>
+      <x:c r="F43" s="26" t="str">
+        <x:v>Given MMSA Field is logged into RB as FR.
+When the user navigates to the Leads object.
+And the user opens the list view selector.
+And the user selects the "Toutes les pistes" list view.
+And the user opens the Filters panel.</x:v>
+      </x:c>
+      <x:c r="G43" s="26" t="str">
+        <x:v>Then the "Toutes les pistes" list view should load successfully and be accessible to the user.
+And the existing filter "Lead Sub Source not equal to PTYA" should be removed.
+And the new filter "Pre-Product Lead equals false" should be present for the applicable Marketing records.
+And the list view should display only records satisfying the updated filter criteria and all other existing filters.</x:v>
+      </x:c>
+      <x:c r="H43" s="26" t="str">
+        <x:v>User Coverage: French MMSA Field
+Shared With: French MMSA Users Group
+Object: Leads
+List View: Toutes les pistes
+List View API Name: Toutes_les_pistes
+Record Type: Marketing (where applicable)
+Removed Filter: Lead Sub Source != PTYA
+New Filter: Pre-Product Lead = false</x:v>
+      </x:c>
+      <x:c r="I43" s="25" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="J43" s="25" t="str">
+        <x:v>Batman</x:v>
+      </x:c>
+      <x:c r="K43" s="25" t="str">
+        <x:v>HOJ</x:v>
+      </x:c>
+      <x:c r="L43" s="26" t="str"/>
+    </x:row>
+    <x:row r="44" ht="130" customHeight="1">
+      <x:c r="A44" s="25" t="str">
+        <x:v>TC-043</x:v>
+      </x:c>
+      <x:c r="B44" s="25" t="str">
+        <x:v>BIGBIRD-3029</x:v>
+      </x:c>
+      <x:c r="C44" s="27" t="str">
+        <x:v>FR</x:v>
+      </x:c>
+      <x:c r="D44" s="26" t="str">
+        <x:v>MMSRB_Fr_DM_LeadsListView_ToutesLesPistes_PreProductLeadFilter</x:v>
+      </x:c>
+      <x:c r="E44" s="26" t="str">
+        <x:v>Verify that the French MMS District Manager user can access the Toutes les pistes list view and that the Lead Sub Source filter is replaced with the Pre-Product Lead filter where applicable to Marketing leads.</x:v>
+      </x:c>
+      <x:c r="F44" s="26" t="str">
+        <x:v>Given MMS District Manager is logged into RB as FR.
+When the user navigates to the Leads object.
+And the user opens the list view selector.
+And the user selects the "Toutes les pistes" list view.
+And the user opens the Filters panel.</x:v>
+      </x:c>
+      <x:c r="G44" s="26" t="str">
+        <x:v>Then the "Toutes les pistes" list view should load successfully and be accessible to the user.
+And the existing filter "Lead Sub Source not equal to PTYA" should be removed.
+And the new filter "Pre-Product Lead equals false" should be present for the applicable Marketing records.
+And the list view should display only records satisfying the updated filter criteria and all other existing filters.</x:v>
+      </x:c>
+      <x:c r="H44" s="26" t="str">
+        <x:v>User Coverage: French MMS District Manager
+Shared With: French SM Users Group
+Object: Leads
+List View: Toutes les pistes
+List View API Name: Toutes_les_pistes
+Record Type: Marketing (where applicable)
+Removed Filter: Lead Sub Source != PTYA
+New Filter: Pre-Product Lead = false</x:v>
+      </x:c>
+      <x:c r="I44" s="25" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="J44" s="25" t="str">
+        <x:v>Batman</x:v>
+      </x:c>
+      <x:c r="K44" s="25" t="str">
+        <x:v>HOJ</x:v>
+      </x:c>
+      <x:c r="L44" s="26" t="str"/>
+    </x:row>
+    <x:row r="45" ht="130" customHeight="1">
+      <x:c r="A45" s="25" t="str">
+        <x:v>TC-044</x:v>
+      </x:c>
+      <x:c r="B45" s="25" t="str">
+        <x:v>BIGBIRD-3029</x:v>
+      </x:c>
+      <x:c r="C45" s="27" t="str">
+        <x:v>EN</x:v>
+      </x:c>
+      <x:c r="D45" s="26" t="str">
+        <x:v>MMSRB_En_AVP_LeadsListView_AllMarketingLeads_PreProductLeadFilter</x:v>
+      </x:c>
+      <x:c r="E45" s="26" t="str">
+        <x:v>Verify that the English MMS AVP user can access the All Leads list view and that the Lead Sub Source filter is replaced with the Pre-Product Lead filter where applicable to Marketing leads.</x:v>
+      </x:c>
+      <x:c r="F45" s="26" t="str">
+        <x:v>Given MMS AVP is logged into RB as EN.
+When the user navigates to the Leads object.
+And the user opens the list view selector.
+And the user selects the "All Leads" list view.
+And the user opens the Filters panel.</x:v>
+      </x:c>
+      <x:c r="G45" s="26" t="str">
+        <x:v>Then the "All Leads" list view should load successfully and be accessible to the user.
+And the existing filter "Lead Sub Source not equal to PTYA" should be removed.
+And the new filter "Pre-Product Lead equals false" should be present for the applicable Marketing records.
+And the list view should display only records satisfying the updated filter criteria and all other existing filters.</x:v>
+      </x:c>
+      <x:c r="H45" s="26" t="str">
+        <x:v>User Coverage: English MMS AVP
+Shared With: English AVP Users Group
+Object: Leads
+List View: All Leads
+List View API Name: All_Marketing_Leads
+Record Type: Marketing (where applicable)
+Removed Filter: Lead Sub Source != PTYA
+New Filter: Pre-Product Lead = false</x:v>
+      </x:c>
+      <x:c r="I45" s="25" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="J45" s="25" t="str">
+        <x:v>Batman</x:v>
+      </x:c>
+      <x:c r="K45" s="25" t="str">
+        <x:v>HOJ</x:v>
+      </x:c>
+      <x:c r="L45" s="26" t="str"/>
+    </x:row>
+    <x:row r="46" ht="130" customHeight="1">
+      <x:c r="A46" s="25" t="str">
+        <x:v>TC-045</x:v>
+      </x:c>
+      <x:c r="B46" s="25" t="str">
+        <x:v>BIGBIRD-3029</x:v>
+      </x:c>
+      <x:c r="C46" s="27" t="str">
+        <x:v>EN</x:v>
+      </x:c>
+      <x:c r="D46" s="26" t="str">
+        <x:v>MMSRB_En_Field_LeadsListView_AllMarketingLeads_PreProductLeadFilter</x:v>
+      </x:c>
+      <x:c r="E46" s="26" t="str">
+        <x:v>Verify that the English MMS Field user can access the All Leads list view and that the Lead Sub Source filter is replaced with the Pre-Product Lead filter where applicable to Marketing leads.</x:v>
+      </x:c>
+      <x:c r="F46" s="26" t="str">
+        <x:v>Given MMS Field is logged into RB as EN.
+When the user navigates to the Leads object.
+And the user opens the list view selector.
+And the user selects the "All Leads" list view.
+And the user opens the Filters panel.</x:v>
+      </x:c>
+      <x:c r="G46" s="26" t="str">
+        <x:v>Then the "All Leads" list view should load successfully and be accessible to the user.
+And the existing filter "Lead Sub Source not equal to PTYA" should be removed.
+And the new filter "Pre-Product Lead equals false" should be present for the applicable Marketing records.
+And the list view should display only records satisfying the updated filter criteria and all other existing filters.</x:v>
+      </x:c>
+      <x:c r="H46" s="26" t="str">
+        <x:v>User Coverage: English MMS Field
+Shared With: English MMS Users Group
+Object: Leads
+List View: All Leads
+List View API Name: All_Marketing_Leads
+Record Type: Marketing (where applicable)
+Removed Filter: Lead Sub Source != PTYA
+New Filter: Pre-Product Lead = false</x:v>
+      </x:c>
+      <x:c r="I46" s="25" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="J46" s="25" t="str">
+        <x:v>Batman</x:v>
+      </x:c>
+      <x:c r="K46" s="25" t="str">
+        <x:v>HOJ</x:v>
+      </x:c>
+      <x:c r="L46" s="26" t="str"/>
+    </x:row>
+    <x:row r="47" ht="130" customHeight="1">
+      <x:c r="A47" s="25" t="str">
+        <x:v>TC-046</x:v>
+      </x:c>
+      <x:c r="B47" s="25" t="str">
+        <x:v>BIGBIRD-3029</x:v>
+      </x:c>
+      <x:c r="C47" s="27" t="str">
+        <x:v>EN</x:v>
+      </x:c>
+      <x:c r="D47" s="26" t="str">
+        <x:v>MMSARB_En_Field_LeadsListView_AllMarketingLeads_PreProductLeadFilter</x:v>
+      </x:c>
+      <x:c r="E47" s="26" t="str">
+        <x:v>Verify that the English MMSA Field user can access the All Leads list view and that the Lead Sub Source filter is replaced with the Pre-Product Lead filter where applicable to Marketing leads.</x:v>
+      </x:c>
+      <x:c r="F47" s="26" t="str">
+        <x:v>Given MMSA Field is logged into RB as EN.
+When the user navigates to the Leads object.
+And the user opens the list view selector.
+And the user selects the "All Leads" list view.
+And the user opens the Filters panel.</x:v>
+      </x:c>
+      <x:c r="G47" s="26" t="str">
+        <x:v>Then the "All Leads" list view should load successfully and be accessible to the user.
+And the existing filter "Lead Sub Source not equal to PTYA" should be removed.
+And the new filter "Pre-Product Lead equals false" should be present for the applicable Marketing records.
+And the list view should display only records satisfying the updated filter criteria and all other existing filters.</x:v>
+      </x:c>
+      <x:c r="H47" s="26" t="str">
+        <x:v>User Coverage: English MMSA Field
+Shared With: English MMSA Users Group
+Object: Leads
+List View: All Leads
+List View API Name: All_Marketing_Leads
+Record Type: Marketing (where applicable)
+Removed Filter: Lead Sub Source != PTYA
+New Filter: Pre-Product Lead = false</x:v>
+      </x:c>
+      <x:c r="I47" s="25" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="J47" s="25" t="str">
+        <x:v>Batman</x:v>
+      </x:c>
+      <x:c r="K47" s="25" t="str">
+        <x:v>HOJ</x:v>
+      </x:c>
+      <x:c r="L47" s="26" t="str"/>
+    </x:row>
+    <x:row r="48" ht="130" customHeight="1">
+      <x:c r="A48" s="25" t="str">
+        <x:v>TC-047</x:v>
+      </x:c>
+      <x:c r="B48" s="25" t="str">
+        <x:v>BIGBIRD-3029</x:v>
+      </x:c>
+      <x:c r="C48" s="27" t="str">
+        <x:v>EN</x:v>
+      </x:c>
+      <x:c r="D48" s="26" t="str">
+        <x:v>MMSRB_En_DM_LeadsListView_AllMarketingLeads_PreProductLeadFilter</x:v>
+      </x:c>
+      <x:c r="E48" s="26" t="str">
+        <x:v>Verify that the English MMS District Manager user can access the All Leads list view and that the Lead Sub Source filter is replaced with the Pre-Product Lead filter where applicable to Marketing leads.</x:v>
+      </x:c>
+      <x:c r="F48" s="26" t="str">
+        <x:v>Given MMS District Manager is logged into RB as EN.
+When the user navigates to the Leads object.
+And the user opens the list view selector.
+And the user selects the "All Leads" list view.
+And the user opens the Filters panel.</x:v>
+      </x:c>
+      <x:c r="G48" s="26" t="str">
+        <x:v>Then the "All Leads" list view should load successfully and be accessible to the user.
+And the existing filter "Lead Sub Source not equal to PTYA" should be removed.
+And the new filter "Pre-Product Lead equals false" should be present for the applicable Marketing records.
+And the list view should display only records satisfying the updated filter criteria and all other existing filters.</x:v>
+      </x:c>
+      <x:c r="H48" s="26" t="str">
+        <x:v>User Coverage: English MMS District Manager
+Shared With: English SM Users Group
+Object: Leads
+List View: All Leads
+List View API Name: All_Marketing_Leads
+Record Type: Marketing (where applicable)
+Removed Filter: Lead Sub Source != PTYA
+New Filter: Pre-Product Lead = false</x:v>
+      </x:c>
+      <x:c r="I48" s="25" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="J48" s="25" t="str">
+        <x:v>Batman</x:v>
+      </x:c>
+      <x:c r="K48" s="25" t="str">
+        <x:v>HOJ</x:v>
+      </x:c>
+      <x:c r="L48" s="26" t="str"/>
+    </x:row>
+    <x:row r="49" ht="130" customHeight="1">
+      <x:c r="A49" s="25" t="str">
+        <x:v>TC-048</x:v>
+      </x:c>
+      <x:c r="B49" s="25" t="str">
+        <x:v>BIGBIRD-3029</x:v>
+      </x:c>
+      <x:c r="C49" s="27" t="str">
+        <x:v>EN</x:v>
+      </x:c>
+      <x:c r="D49" s="26" t="str">
+        <x:v>MMSRB_En_AVP_LeadsListView_HOJOpenReferralsForMMS_PreProductLeadFilter</x:v>
+      </x:c>
+      <x:c r="E49" s="26" t="str">
+        <x:v>Verify that the English MMS AVP user can access the My Branch Referrals list view and that the Lead Sub Source filter is replaced with the Pre-Product Lead filter where applicable to Marketing leads.</x:v>
+      </x:c>
+      <x:c r="F49" s="26" t="str">
+        <x:v>Given MMS AVP is logged into RB as EN.
+When the user navigates to the Leads object.
+And the user opens the list view selector.
+And the user selects the "My Branch Referrals" list view.
+And the user opens the Filters panel.</x:v>
+      </x:c>
+      <x:c r="G49" s="26" t="str">
+        <x:v>Then the "My Branch Referrals" list view should load successfully and be accessible to the user.
+And the existing filter "Lead Sub Source not equal to PTYA" should be removed.
+And the new filter "Pre-Product Lead equals false" should be present for the applicable Marketing records.
+And the list view should display only records satisfying the updated filter criteria and all other existing filters.</x:v>
+      </x:c>
+      <x:c r="H49" s="26" t="str">
+        <x:v>User Coverage: English MMS AVP
+Shared With: English AVP Users Group
+Object: Leads
+List View: My Branch Referrals
+List View API Name: HOJ_Open_referrals_for_MMS
+Record Type: Marketing (where applicable)
+Removed Filter: Lead Sub Source != PTYA
+New Filter: Pre-Product Lead = false</x:v>
+      </x:c>
+      <x:c r="I49" s="25" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="J49" s="25" t="str">
+        <x:v>Batman</x:v>
+      </x:c>
+      <x:c r="K49" s="25" t="str">
+        <x:v>HOJ</x:v>
+      </x:c>
+      <x:c r="L49" s="26" t="str"/>
+    </x:row>
+    <x:row r="50" ht="130" customHeight="1">
+      <x:c r="A50" s="25" t="str">
+        <x:v>TC-049</x:v>
+      </x:c>
+      <x:c r="B50" s="25" t="str">
+        <x:v>BIGBIRD-3029</x:v>
+      </x:c>
+      <x:c r="C50" s="27" t="str">
+        <x:v>EN</x:v>
+      </x:c>
+      <x:c r="D50" s="26" t="str">
+        <x:v>MMSRB_En_Field_LeadsListView_HOJOpenReferralsForMMS_PreProductLeadFilter</x:v>
+      </x:c>
+      <x:c r="E50" s="26" t="str">
+        <x:v>Verify that the English MMS Field user can access the My Branch Referrals list view and that the Lead Sub Source filter is replaced with the Pre-Product Lead filter where applicable to Marketing leads.</x:v>
+      </x:c>
+      <x:c r="F50" s="26" t="str">
+        <x:v>Given MMS Field is logged into RB as EN.
+When the user navigates to the Leads object.
+And the user opens the list view selector.
+And the user selects the "My Branch Referrals" list view.
+And the user opens the Filters panel.</x:v>
+      </x:c>
+      <x:c r="G50" s="26" t="str">
+        <x:v>Then the "My Branch Referrals" list view should load successfully and be accessible to the user.
+And the existing filter "Lead Sub Source not equal to PTYA" should be removed.
+And the new filter "Pre-Product Lead equals false" should be present for the applicable Marketing records.
+And the list view should display only records satisfying the updated filter criteria and all other existing filters.</x:v>
+      </x:c>
+      <x:c r="H50" s="26" t="str">
+        <x:v>User Coverage: English MMS Field
+Shared With: English MMS Users Group
+Object: Leads
+List View: My Branch Referrals
+List View API Name: HOJ_Open_referrals_for_MMS
+Record Type: Marketing (where applicable)
+Removed Filter: Lead Sub Source != PTYA
+New Filter: Pre-Product Lead = false</x:v>
+      </x:c>
+      <x:c r="I50" s="25" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="J50" s="25" t="str">
+        <x:v>Batman</x:v>
+      </x:c>
+      <x:c r="K50" s="25" t="str">
+        <x:v>HOJ</x:v>
+      </x:c>
+      <x:c r="L50" s="26" t="str"/>
+    </x:row>
+    <x:row r="51" ht="130" customHeight="1">
+      <x:c r="A51" s="25" t="str">
+        <x:v>TC-050</x:v>
+      </x:c>
+      <x:c r="B51" s="25" t="str">
+        <x:v>BIGBIRD-3029</x:v>
+      </x:c>
+      <x:c r="C51" s="27" t="str">
+        <x:v>EN</x:v>
+      </x:c>
+      <x:c r="D51" s="26" t="str">
+        <x:v>MMSARB_En_Field_LeadsListView_HOJOpenReferralsForMMS_PreProductLeadFilter</x:v>
+      </x:c>
+      <x:c r="E51" s="26" t="str">
+        <x:v>Verify that the English MMSA Field user can access the My Branch Referrals list view and that the Lead Sub Source filter is replaced with the Pre-Product Lead filter where applicable to Marketing leads.</x:v>
+      </x:c>
+      <x:c r="F51" s="26" t="str">
+        <x:v>Given MMSA Field is logged into RB as EN.
+When the user navigates to the Leads object.
+And the user opens the list view selector.
+And the user selects the "My Branch Referrals" list view.
+And the user opens the Filters panel.</x:v>
+      </x:c>
+      <x:c r="G51" s="26" t="str">
+        <x:v>Then the "My Branch Referrals" list view should load successfully and be accessible to the user.
+And the existing filter "Lead Sub Source not equal to PTYA" should be removed.
+And the new filter "Pre-Product Lead equals false" should be present for the applicable Marketing records.
+And the list view should display only records satisfying the updated filter criteria and all other existing filters.</x:v>
+      </x:c>
+      <x:c r="H51" s="26" t="str">
+        <x:v>User Coverage: English MMSA Field
+Shared With: English MMSA Users Group
+Object: Leads
+List View: My Branch Referrals
+List View API Name: HOJ_Open_referrals_for_MMS
+Record Type: Marketing (where applicable)
+Removed Filter: Lead Sub Source != PTYA
+New Filter: Pre-Product Lead = false</x:v>
+      </x:c>
+      <x:c r="I51" s="25" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="J51" s="25" t="str">
+        <x:v>Batman</x:v>
+      </x:c>
+      <x:c r="K51" s="25" t="str">
+        <x:v>HOJ</x:v>
+      </x:c>
+      <x:c r="L51" s="26" t="str"/>
+    </x:row>
+    <x:row r="52" ht="130" customHeight="1">
+      <x:c r="A52" s="25" t="str">
+        <x:v>TC-051</x:v>
+      </x:c>
+      <x:c r="B52" s="25" t="str">
+        <x:v>BIGBIRD-3029</x:v>
+      </x:c>
+      <x:c r="C52" s="27" t="str">
+        <x:v>EN</x:v>
+      </x:c>
+      <x:c r="D52" s="26" t="str">
+        <x:v>MMSRB_En_DM_LeadsListView_HOJOpenReferralsForMMS_PreProductLeadFilter</x:v>
+      </x:c>
+      <x:c r="E52" s="26" t="str">
+        <x:v>Verify that the English MMS District Manager user can access the My Branch Referrals list view and that the Lead Sub Source filter is replaced with the Pre-Product Lead filter where applicable to Marketing leads.</x:v>
+      </x:c>
+      <x:c r="F52" s="26" t="str">
+        <x:v>Given MMS District Manager is logged into RB as EN.
+When the user navigates to the Leads object.
+And the user opens the list view selector.
+And the user selects the "My Branch Referrals" list view.
+And the user opens the Filters panel.</x:v>
+      </x:c>
+      <x:c r="G52" s="26" t="str">
+        <x:v>Then the "My Branch Referrals" list view should load successfully and be accessible to the user.
+And the existing filter "Lead Sub Source not equal to PTYA" should be removed.
+And the new filter "Pre-Product Lead equals false" should be present for the applicable Marketing records.
+And the list view should display only records satisfying the updated filter criteria and all other existing filters.</x:v>
+      </x:c>
+      <x:c r="H52" s="26" t="str">
+        <x:v>User Coverage: English MMS District Manager
+Shared With: English SM Users Group
+Object: Leads
+List View: My Branch Referrals
+List View API Name: HOJ_Open_referrals_for_MMS
+Record Type: Marketing (where applicable)
+Removed Filter: Lead Sub Source != PTYA
+New Filter: Pre-Product Lead = false</x:v>
+      </x:c>
+      <x:c r="I52" s="25" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="J52" s="25" t="str">
+        <x:v>Batman</x:v>
+      </x:c>
+      <x:c r="K52" s="25" t="str">
+        <x:v>HOJ</x:v>
+      </x:c>
+      <x:c r="L52" s="26" t="str"/>
+    </x:row>
+    <x:row r="53" ht="130" customHeight="1">
+      <x:c r="A53" s="25" t="str">
+        <x:v>TC-052</x:v>
+      </x:c>
+      <x:c r="B53" s="25" t="str">
+        <x:v>BIGBIRD-3029</x:v>
+      </x:c>
+      <x:c r="C53" s="27" t="str">
+        <x:v>FR</x:v>
+      </x:c>
+      <x:c r="D53" s="26" t="str">
+        <x:v>MMSRB_Fr_AVP_LeadsListView_HOJOpenReferralsForMMSFrench_PreProductLeadFilter</x:v>
+      </x:c>
+      <x:c r="E53" s="26" t="str">
+        <x:v>Verify that the French MMS AVP user can access the Mes recommandations de la succursale list view and that the Lead Sub Source filter is replaced with the Pre-Product Lead filter where applicable to Marketing leads.</x:v>
+      </x:c>
+      <x:c r="F53" s="26" t="str">
+        <x:v>Given MMS AVP is logged into RB as FR.
+When the user navigates to the Leads object.
+And the user opens the list view selector.
+And the user selects the "Mes recommandations de la succursale" list view.
+And the user opens the Filters panel.</x:v>
+      </x:c>
+      <x:c r="G53" s="26" t="str">
+        <x:v>Then the "Mes recommandations de la succursale" list view should load successfully and be accessible to the user.
+And the existing filter "Lead Sub Source not equal to PTYA" should be removed.
+And the new filter "Pre-Product Lead equals false" should be present for the applicable Marketing records.
+And the list view should display only records satisfying the updated filter criteria and all other existing filters.</x:v>
+      </x:c>
+      <x:c r="H53" s="26" t="str">
+        <x:v>User Coverage: French MMS AVP
+Shared With: French AVP Users Group
+Object: Leads
+List View: Mes recommandations de la succursale
+List View API Name: HOJ_Open_referrals_for_MMS_French
+Record Type: Marketing (where applicable)
+Removed Filter: Lead Sub Source != PTYA
+New Filter: Pre-Product Lead = false</x:v>
+      </x:c>
+      <x:c r="I53" s="25" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="J53" s="25" t="str">
+        <x:v>Batman</x:v>
+      </x:c>
+      <x:c r="K53" s="25" t="str">
+        <x:v>HOJ</x:v>
+      </x:c>
+      <x:c r="L53" s="26" t="str"/>
+    </x:row>
+    <x:row r="54" ht="130" customHeight="1">
+      <x:c r="A54" s="25" t="str">
+        <x:v>TC-053</x:v>
+      </x:c>
+      <x:c r="B54" s="25" t="str">
+        <x:v>BIGBIRD-3029</x:v>
+      </x:c>
+      <x:c r="C54" s="27" t="str">
+        <x:v>FR</x:v>
+      </x:c>
+      <x:c r="D54" s="26" t="str">
+        <x:v>MMSRB_Fr_Field_LeadsListView_HOJOpenReferralsForMMSFrench_PreProductLeadFilter</x:v>
+      </x:c>
+      <x:c r="E54" s="26" t="str">
+        <x:v>Verify that the French MMS Field user can access the Mes recommandations de la succursale list view and that the Lead Sub Source filter is replaced with the Pre-Product Lead filter where applicable to Marketing leads.</x:v>
+      </x:c>
+      <x:c r="F54" s="26" t="str">
+        <x:v>Given MMS Field is logged into RB as FR.
+When the user navigates to the Leads object.
+And the user opens the list view selector.
+And the user selects the "Mes recommandations de la succursale" list view.
+And the user opens the Filters panel.</x:v>
+      </x:c>
+      <x:c r="G54" s="26" t="str">
+        <x:v>Then the "Mes recommandations de la succursale" list view should load successfully and be accessible to the user.
+And the existing filter "Lead Sub Source not equal to PTYA" should be removed.
+And the new filter "Pre-Product Lead equals false" should be present for the applicable Marketing records.
+And the list view should display only records satisfying the updated filter criteria and all other existing filters.</x:v>
+      </x:c>
+      <x:c r="H54" s="26" t="str">
+        <x:v>User Coverage: French MMS Field
+Shared With: French MMS Users Group
+Object: Leads
+List View: Mes recommandations de la succursale
+List View API Name: HOJ_Open_referrals_for_MMS_French
+Record Type: Marketing (where applicable)
+Removed Filter: Lead Sub Source != PTYA
+New Filter: Pre-Product Lead = false</x:v>
+      </x:c>
+      <x:c r="I54" s="25" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="J54" s="25" t="str">
+        <x:v>Batman</x:v>
+      </x:c>
+      <x:c r="K54" s="25" t="str">
+        <x:v>HOJ</x:v>
+      </x:c>
+      <x:c r="L54" s="26" t="str"/>
+    </x:row>
+    <x:row r="55" ht="130" customHeight="1">
+      <x:c r="A55" s="25" t="str">
+        <x:v>TC-054</x:v>
+      </x:c>
+      <x:c r="B55" s="25" t="str">
+        <x:v>BIGBIRD-3029</x:v>
+      </x:c>
+      <x:c r="C55" s="27" t="str">
+        <x:v>FR</x:v>
+      </x:c>
+      <x:c r="D55" s="26" t="str">
+        <x:v>MMSARB_Fr_Field_LeadsListView_HOJOpenReferralsForMMSFrench_PreProductLeadFilter</x:v>
+      </x:c>
+      <x:c r="E55" s="26" t="str">
+        <x:v>Verify that the French MMSA Field user can access the Mes recommandations de la succursale list view and that the Lead Sub Source filter is replaced with the Pre-Product Lead filter where applicable to Marketing leads.</x:v>
+      </x:c>
+      <x:c r="F55" s="26" t="str">
+        <x:v>Given MMSA Field is logged into RB as FR.
+When the user navigates to the Leads object.
+And the user opens the list view selector.
+And the user selects the "Mes recommandations de la succursale" list view.
+And the user opens the Filters panel.</x:v>
+      </x:c>
+      <x:c r="G55" s="26" t="str">
+        <x:v>Then the "Mes recommandations de la succursale" list view should load successfully and be accessible to the user.
+And the existing filter "Lead Sub Source not equal to PTYA" should be removed.
+And the new filter "Pre-Product Lead equals false" should be present for the applicable Marketing records.
+And the list view should display only records satisfying the updated filter criteria and all other existing filters.</x:v>
+      </x:c>
+      <x:c r="H55" s="26" t="str">
+        <x:v>User Coverage: French MMSA Field
+Shared With: French MMSA Users Group
+Object: Leads
+List View: Mes recommandations de la succursale
+List View API Name: HOJ_Open_referrals_for_MMS_French
+Record Type: Marketing (where applicable)
+Removed Filter: Lead Sub Source != PTYA
+New Filter: Pre-Product Lead = false</x:v>
+      </x:c>
+      <x:c r="I55" s="25" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="J55" s="25" t="str">
+        <x:v>Batman</x:v>
+      </x:c>
+      <x:c r="K55" s="25" t="str">
+        <x:v>HOJ</x:v>
+      </x:c>
+      <x:c r="L55" s="26" t="str"/>
+    </x:row>
+    <x:row r="56" ht="130" customHeight="1">
+      <x:c r="A56" s="25" t="str">
+        <x:v>TC-055</x:v>
+      </x:c>
+      <x:c r="B56" s="25" t="str">
+        <x:v>BIGBIRD-3029</x:v>
+      </x:c>
+      <x:c r="C56" s="27" t="str">
+        <x:v>FR</x:v>
+      </x:c>
+      <x:c r="D56" s="26" t="str">
+        <x:v>MMSRB_Fr_DM_LeadsListView_HOJOpenReferralsForMMSFrench_PreProductLeadFilter</x:v>
+      </x:c>
+      <x:c r="E56" s="26" t="str">
+        <x:v>Verify that the French MMS District Manager user can access the Mes recommandations de la succursale list view and that the Lead Sub Source filter is replaced with the Pre-Product Lead filter where applicable to Marketing leads.</x:v>
+      </x:c>
+      <x:c r="F56" s="26" t="str">
+        <x:v>Given MMS District Manager is logged into RB as FR.
+When the user navigates to the Leads object.
+And the user opens the list view selector.
+And the user selects the "Mes recommandations de la succursale" list view.
+And the user opens the Filters panel.</x:v>
+      </x:c>
+      <x:c r="G56" s="26" t="str">
+        <x:v>Then the "Mes recommandations de la succursale" list view should load successfully and be accessible to the user.
+And the existing filter "Lead Sub Source not equal to PTYA" should be removed.
+And the new filter "Pre-Product Lead equals false" should be present for the applicable Marketing records.
+And the list view should display only records satisfying the updated filter criteria and all other existing filters.</x:v>
+      </x:c>
+      <x:c r="H56" s="26" t="str">
+        <x:v>User Coverage: French MMS District Manager
+Shared With: French SM Users Group
+Object: Leads
+List View: Mes recommandations de la succursale
+List View API Name: HOJ_Open_referrals_for_MMS_French
+Record Type: Marketing (where applicable)
+Removed Filter: Lead Sub Source != PTYA
+New Filter: Pre-Product Lead = false</x:v>
+      </x:c>
+      <x:c r="I56" s="25" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="J56" s="25" t="str">
+        <x:v>Batman</x:v>
+      </x:c>
+      <x:c r="K56" s="25" t="str">
+        <x:v>HOJ</x:v>
+      </x:c>
+      <x:c r="L56" s="26" t="str"/>
+    </x:row>
+    <x:row r="57" ht="130" customHeight="1">
+      <x:c r="A57" s="25" t="str">
+        <x:v>TC-056</x:v>
+      </x:c>
+      <x:c r="B57" s="25" t="str">
+        <x:v>BIGBIRD-3029</x:v>
+      </x:c>
+      <x:c r="C57" s="27" t="str">
+        <x:v>FR</x:v>
+      </x:c>
+      <x:c r="D57" s="26" t="str">
+        <x:v>MMSRB_Fr_AVP_LeadsListView_LesRecommandationsDeLaSuccursaleDe_PreProductLeadFilter</x:v>
+      </x:c>
+      <x:c r="E57" s="26" t="str">
+        <x:v>Verify that the French MMS AVP user can access the Recommandations des succ. à m... list view and that the Lead Sub Source filter is replaced with the Pre-Product Lead filter where applicable to Marketing leads.</x:v>
+      </x:c>
+      <x:c r="F57" s="26" t="str">
+        <x:v>Given MMS AVP is logged into RB as FR.
+When the user navigates to the Leads object.
+And the user opens the list view selector.
+And the user selects the "Recommandations des succ. à m..." list view.
+And the user opens the Filters panel.</x:v>
+      </x:c>
+      <x:c r="G57" s="26" t="str">
+        <x:v>Then the "Recommandations des succ. à m..." list view should load successfully and be accessible to the user.
+And the existing filter "Lead Sub Source not equal to PTYA" should be removed.
+And the new filter "Pre-Product Lead equals false" should be present for the applicable Marketing records.
+And the list view should display only records satisfying the updated filter criteria and all other existing filters.</x:v>
+      </x:c>
+      <x:c r="H57" s="26" t="str">
+        <x:v>User Coverage: French MMS AVP
+Shared With: French AVP Users Group
+Object: Leads
+List View: Recommandations des succ. à m...
+List View API Name: Les_recommandations_de_la_succursale_de
+Record Type: Marketing (where applicable)
+Removed Filter: Lead Sub Source != PTYA
+New Filter: Pre-Product Lead = false</x:v>
+      </x:c>
+      <x:c r="I57" s="25" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="J57" s="25" t="str">
+        <x:v>Batman</x:v>
+      </x:c>
+      <x:c r="K57" s="25" t="str">
+        <x:v>HOJ</x:v>
+      </x:c>
+      <x:c r="L57" s="26" t="str"/>
+    </x:row>
+    <x:row r="58" ht="130" customHeight="1">
+      <x:c r="A58" s="25" t="str">
+        <x:v>TC-057</x:v>
+      </x:c>
+      <x:c r="B58" s="25" t="str">
+        <x:v>BIGBIRD-3029</x:v>
+      </x:c>
+      <x:c r="C58" s="27" t="str">
+        <x:v>FR</x:v>
+      </x:c>
+      <x:c r="D58" s="26" t="str">
+        <x:v>MMSRB_Fr_DM_LeadsListView_LesRecommandationsDeLaSuccursaleDe_PreProductLeadFilter</x:v>
+      </x:c>
+      <x:c r="E58" s="26" t="str">
+        <x:v>Verify that the French MMS District Manager user can access the Recommandations des succ. à m... list view and that the Lead Sub Source filter is replaced with the Pre-Product Lead filter where applicable to Marketing leads.</x:v>
+      </x:c>
+      <x:c r="F58" s="26" t="str">
+        <x:v>Given MMS District Manager is logged into RB as FR.
+When the user navigates to the Leads object.
+And the user opens the list view selector.
+And the user selects the "Recommandations des succ. à m..." list view.
+And the user opens the Filters panel.</x:v>
+      </x:c>
+      <x:c r="G58" s="26" t="str">
+        <x:v>Then the "Recommandations des succ. à m..." list view should load successfully and be accessible to the user.
+And the existing filter "Lead Sub Source not equal to PTYA" should be removed.
+And the new filter "Pre-Product Lead equals false" should be present for the applicable Marketing records.
+And the list view should display only records satisfying the updated filter criteria and all other existing filters.</x:v>
+      </x:c>
+      <x:c r="H58" s="26" t="str">
+        <x:v>User Coverage: French MMS District Manager
+Shared With: French SM Users Group
+Object: Leads
+List View: Recommandations des succ. à m...
+List View API Name: Les_recommandations_de_la_succursale_de
+Record Type: Marketing (where applicable)
+Removed Filter: Lead Sub Source != PTYA
+New Filter: Pre-Product Lead = false</x:v>
+      </x:c>
+      <x:c r="I58" s="25" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="J58" s="25" t="str">
+        <x:v>Batman</x:v>
+      </x:c>
+      <x:c r="K58" s="25" t="str">
+        <x:v>HOJ</x:v>
+      </x:c>
+      <x:c r="L58" s="26" t="str"/>
+    </x:row>
+    <x:row r="59" ht="130" customHeight="1">
+      <x:c r="A59" s="25" t="str">
+        <x:v>TC-058</x:v>
+      </x:c>
+      <x:c r="B59" s="25" t="str">
+        <x:v>BIGBIRD-3029</x:v>
+      </x:c>
+      <x:c r="C59" s="27" t="str">
+        <x:v>EN</x:v>
+      </x:c>
+      <x:c r="D59" s="26" t="str">
+        <x:v>RetailRB_En_BM_LeadsListView_MyBranchLeads_PreProductLeadFilter</x:v>
+      </x:c>
+      <x:c r="E59" s="26" t="str">
+        <x:v>Verify that the English Retail Manager user can access the Branch Leads list view and that the Lead Sub Source filter is replaced with the Pre-Product Lead filter where applicable to Marketing leads.</x:v>
+      </x:c>
+      <x:c r="F59" s="26" t="str">
+        <x:v>Given Retail Manager is logged into RB as EN.
+When the user navigates to the Leads object.
+And the user opens the list view selector.
+And the user selects the "Branch Leads" list view.
+And the user opens the Filters panel.</x:v>
+      </x:c>
+      <x:c r="G59" s="26" t="str">
+        <x:v>Then the "Branch Leads" list view should load successfully and be accessible to the user.
+And the existing filter "Lead Sub Source not equal to PTYA" should be removed.
+And the new filter "Pre-Product Lead equals false" should be present for the applicable Marketing records.
+And the list view should display only records satisfying the updated filter criteria and all other existing filters.</x:v>
+      </x:c>
+      <x:c r="H59" s="26" t="str">
+        <x:v>User Coverage: English Retail Manager
+Shared With: English Branch Manager Users Group
+Object: Leads
+List View: Branch Leads
+List View API Name: My_Branch_Leads
+Record Type: Marketing (where applicable)
+Removed Filter: Lead Sub Source != PTYA
+New Filter: Pre-Product Lead = false</x:v>
+      </x:c>
+      <x:c r="I59" s="25" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="J59" s="25" t="str">
+        <x:v>Batman</x:v>
+      </x:c>
+      <x:c r="K59" s="25" t="str">
+        <x:v>HOJ</x:v>
+      </x:c>
+      <x:c r="L59" s="26" t="str"/>
+    </x:row>
+    <x:row r="60" ht="130" customHeight="1">
+      <x:c r="A60" s="25" t="str">
+        <x:v>TC-059</x:v>
+      </x:c>
+      <x:c r="B60" s="25" t="str">
+        <x:v>BIGBIRD-3029</x:v>
+      </x:c>
+      <x:c r="C60" s="27" t="str">
+        <x:v>EN</x:v>
+      </x:c>
+      <x:c r="D60" s="26" t="str">
+        <x:v>RetailRB_En_Admin_LeadsListView_MyBranchLeads_PreProductLeadFilter</x:v>
+      </x:c>
+      <x:c r="E60" s="26" t="str">
+        <x:v>Verify that the English Retail Admin user can access the Branch Leads list view and that the Lead Sub Source filter is replaced with the Pre-Product Lead filter where applicable to Marketing leads.</x:v>
+      </x:c>
+      <x:c r="F60" s="26" t="str">
+        <x:v>Given Retail Admin is logged into RB as EN.
+When the user navigates to the Leads object.
+And the user opens the list view selector.
+And the user selects the "Branch Leads" list view.
+And the user opens the Filters panel.</x:v>
+      </x:c>
+      <x:c r="G60" s="26" t="str">
+        <x:v>Then the "Branch Leads" list view should load successfully and be accessible to the user.
+And the existing filter "Lead Sub Source not equal to PTYA" should be removed.
+And the new filter "Pre-Product Lead equals false" should be present for the applicable Marketing records.
+And the list view should display only records satisfying the updated filter criteria and all other existing filters.</x:v>
+      </x:c>
+      <x:c r="H60" s="26" t="str">
+        <x:v>User Coverage: English Retail Admin
+Shared With: English Business Admins Group
+Object: Leads
+List View: Branch Leads
+List View API Name: My_Branch_Leads
+Record Type: Marketing (where applicable)
+Removed Filter: Lead Sub Source != PTYA
+New Filter: Pre-Product Lead = false</x:v>
+      </x:c>
+      <x:c r="I60" s="25" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="J60" s="25" t="str">
+        <x:v>Batman</x:v>
+      </x:c>
+      <x:c r="K60" s="25" t="str">
+        <x:v>HOJ</x:v>
+      </x:c>
+      <x:c r="L60" s="26" t="str"/>
+    </x:row>
+    <x:row r="61" ht="130" customHeight="1">
+      <x:c r="A61" s="25" t="str">
+        <x:v>TC-060</x:v>
+      </x:c>
+      <x:c r="B61" s="25" t="str">
+        <x:v>BIGBIRD-3029</x:v>
+      </x:c>
+      <x:c r="C61" s="27" t="str">
+        <x:v>EN</x:v>
+      </x:c>
+      <x:c r="D61" s="26" t="str">
+        <x:v>RetailRB_En_BM_LeadsListView_UnassignedLeads_PreProductLeadFilter</x:v>
+      </x:c>
+      <x:c r="E61" s="26" t="str">
+        <x:v>Verify that the English Retail Manager user can access the Unassigned Leads list view and that the Lead Sub Source filter is replaced with the Pre-Product Lead filter where applicable to Marketing leads.</x:v>
+      </x:c>
+      <x:c r="F61" s="26" t="str">
+        <x:v>Given Retail Manager is logged into RB as EN.
+When the user navigates to the Leads object.
+And the user opens the list view selector.
+And the user selects the "Unassigned Leads" list view.
+And the user opens the Filters panel.</x:v>
+      </x:c>
+      <x:c r="G61" s="26" t="str">
+        <x:v>Then the "Unassigned Leads" list view should load successfully and be accessible to the user.
+And the existing filter "Lead Sub Source not equal to PTYA" should be removed.
+And the new filter "Pre-Product Lead equals false" should be present for the applicable Marketing records.
+And the list view should display only records satisfying the updated filter criteria and all other existing filters.</x:v>
+      </x:c>
+      <x:c r="H61" s="26" t="str">
+        <x:v>User Coverage: English Retail Manager
+Shared With: English Branch Manager Users Group
+Object: Leads
+List View: Unassigned Leads
+List View API Name: My_Relationships_Unassigned_Leads_Lead
+Record Type: Marketing (where applicable)
+Removed Filter: Lead Sub Source != PTYA
+New Filter: Pre-Product Lead = false</x:v>
+      </x:c>
+      <x:c r="I61" s="25" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="J61" s="25" t="str">
+        <x:v>Batman</x:v>
+      </x:c>
+      <x:c r="K61" s="25" t="str">
+        <x:v>HOJ</x:v>
+      </x:c>
+      <x:c r="L61" s="26" t="str"/>
+    </x:row>
+    <x:row r="62" ht="130" customHeight="1">
+      <x:c r="A62" s="25" t="str">
+        <x:v>TC-061</x:v>
+      </x:c>
+      <x:c r="B62" s="25" t="str">
+        <x:v>BIGBIRD-3029</x:v>
+      </x:c>
+      <x:c r="C62" s="27" t="str">
+        <x:v>EN</x:v>
+      </x:c>
+      <x:c r="D62" s="26" t="str">
+        <x:v>RetailRB_En_Admin_LeadsListView_UnassignedLeads_PreProductLeadFilter</x:v>
+      </x:c>
+      <x:c r="E62" s="26" t="str">
+        <x:v>Verify that the English Retail Admin user can access the Unassigned Leads list view and that the Lead Sub Source filter is replaced with the Pre-Product Lead filter where applicable to Marketing leads.</x:v>
+      </x:c>
+      <x:c r="F62" s="26" t="str">
+        <x:v>Given Retail Admin is logged into RB as EN.
+When the user navigates to the Leads object.
+And the user opens the list view selector.
+And the user selects the "Unassigned Leads" list view.
+And the user opens the Filters panel.</x:v>
+      </x:c>
+      <x:c r="G62" s="26" t="str">
+        <x:v>Then the "Unassigned Leads" list view should load successfully and be accessible to the user.
+And the existing filter "Lead Sub Source not equal to PTYA" should be removed.
+And the new filter "Pre-Product Lead equals false" should be present for the applicable Marketing records.
+And the list view should display only records satisfying the updated filter criteria and all other existing filters.</x:v>
+      </x:c>
+      <x:c r="H62" s="26" t="str">
+        <x:v>User Coverage: English Retail Admin
+Shared With: English Business Admins Group
+Object: Leads
+List View: Unassigned Leads
+List View API Name: My_Relationships_Unassigned_Leads_Lead
+Record Type: Marketing (where applicable)
+Removed Filter: Lead Sub Source != PTYA
+New Filter: Pre-Product Lead = false</x:v>
+      </x:c>
+      <x:c r="I62" s="25" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="J62" s="25" t="str">
+        <x:v>Batman</x:v>
+      </x:c>
+      <x:c r="K62" s="25" t="str">
+        <x:v>HOJ</x:v>
+      </x:c>
+      <x:c r="L62" s="26" t="str"/>
+    </x:row>
+    <x:row r="63" ht="130" customHeight="1">
+      <x:c r="A63" s="25" t="str">
+        <x:v>TC-062</x:v>
+      </x:c>
+      <x:c r="B63" s="25" t="str">
+        <x:v>BIGBIRD-3029</x:v>
+      </x:c>
+      <x:c r="C63" s="27" t="str">
+        <x:v>EN</x:v>
+      </x:c>
+      <x:c r="D63" s="26" t="str">
+        <x:v>RSGRB_En_TL_LeadsListView_RSGMySelfGeneratedLeads_PreProductLeadFilter</x:v>
+      </x:c>
+      <x:c r="E63" s="26" t="str">
+        <x:v>Verify that the English RSG Team Leader user can access the My Self Generated Leads list view and that the Lead Sub Source filter is replaced with the Pre-Product Lead filter where applicable to Marketing leads.</x:v>
+      </x:c>
+      <x:c r="F63" s="26" t="str">
+        <x:v>Given RSG Team Leader is logged into RB as EN.
+When the user navigates to the Leads object.
+And the user opens the list view selector.
+And the user selects the "My Self Generated Leads" list view.
+And the user opens the Filters panel.</x:v>
+      </x:c>
+      <x:c r="G63" s="26" t="str">
+        <x:v>Then the "My Self Generated Leads" list view should load successfully and be accessible to the user.
+And the existing filter "Lead Sub Source not equal to PTYA" should be removed.
+And the new filter "Pre-Product Lead equals false" should be present for the applicable Marketing records.
+And the list view should display only records satisfying the updated filter criteria and all other existing filters.</x:v>
+      </x:c>
+      <x:c r="H63" s="26" t="str">
+        <x:v>User Coverage: English RSG Team Leader
+Shared With: English PCMR Manager Users Group
+Object: Leads
+List View: My Self Generated Leads
+List View API Name: RSG_My_Self_Generated_Leads
+Record Type: Marketing (where applicable)
+Removed Filter: Lead Sub Source != PTYA
+New Filter: Pre-Product Lead = false</x:v>
+      </x:c>
+      <x:c r="I63" s="25" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="J63" s="25" t="str">
+        <x:v>Batman</x:v>
+      </x:c>
+      <x:c r="K63" s="25" t="str">
+        <x:v>HOJ</x:v>
+      </x:c>
+      <x:c r="L63" s="26" t="str"/>
+    </x:row>
+    <x:row r="64" ht="130" customHeight="1">
+      <x:c r="A64" s="25" t="str">
+        <x:v>TC-063</x:v>
+      </x:c>
+      <x:c r="B64" s="25" t="str">
+        <x:v>BIGBIRD-3029</x:v>
+      </x:c>
+      <x:c r="C64" s="27" t="str">
+        <x:v>EN</x:v>
+      </x:c>
+      <x:c r="D64" s="26" t="str">
+        <x:v>RSGRB_En_PC_LeadsListView_RSGMySelfGeneratedLeads_PreProductLeadFilter</x:v>
+      </x:c>
+      <x:c r="E64" s="26" t="str">
+        <x:v>Verify that the English RSG Phone Concierge user can access the My Self Generated Leads list view and that the Lead Sub Source filter is replaced with the Pre-Product Lead filter where applicable to Marketing leads.</x:v>
+      </x:c>
+      <x:c r="F64" s="26" t="str">
+        <x:v>Given RSG Phone Concierge is logged into RB as EN.
+When the user navigates to the Leads object.
+And the user opens the list view selector.
+And the user selects the "My Self Generated Leads" list view.
+And the user opens the Filters panel.</x:v>
+      </x:c>
+      <x:c r="G64" s="26" t="str">
+        <x:v>Then the "My Self Generated Leads" list view should load successfully and be accessible to the user.
+And the existing filter "Lead Sub Source not equal to PTYA" should be removed.
+And the new filter "Pre-Product Lead equals false" should be present for the applicable Marketing records.
+And the list view should display only records satisfying the updated filter criteria and all other existing filters.</x:v>
+      </x:c>
+      <x:c r="H64" s="26" t="str">
+        <x:v>User Coverage: English RSG Phone Concierge
+Shared With: English Phone Concierge Users Group
+Object: Leads
+List View: My Self Generated Leads
+List View API Name: RSG_My_Self_Generated_Leads
+Record Type: Marketing (where applicable)
+Removed Filter: Lead Sub Source != PTYA
+New Filter: Pre-Product Lead = false</x:v>
+      </x:c>
+      <x:c r="I64" s="25" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="J64" s="25" t="str">
+        <x:v>Batman</x:v>
+      </x:c>
+      <x:c r="K64" s="25" t="str">
+        <x:v>HOJ</x:v>
+      </x:c>
+      <x:c r="L64" s="26" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6ea1b066367048cc"/>
+  </x:tableParts>
 </x:worksheet>
 </file>